--- a/frontend/src/assets/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet (2).xlsx
+++ b/frontend/src/assets/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet (2).xlsx
@@ -5,13 +5,13 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SebastianCheng\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\christop\AGAP Portal\frontend\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F2802F-E116-486B-98D0-CC9D26BD07CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C414E7D1-C6AB-4455-A8FC-25ED0B4893C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="404">
   <si>
     <t xml:space="preserve">        </t>
   </si>
@@ -1370,127 +1370,7 @@
     <t xml:space="preserve">                               CS FORM 212 (Revised 2025), Page 1 of 4</t>
   </si>
   <si>
-    <t>Avenido</t>
-  </si>
-  <si>
-    <t>Llanes</t>
-  </si>
-  <si>
-    <t>Batangas</t>
-  </si>
-  <si>
-    <t>Lipa</t>
-  </si>
-  <si>
-    <t>4217</t>
-  </si>
-  <si>
-    <t>09169310247</t>
-  </si>
-  <si>
-    <t>avenidoca24@gmail.com</t>
-  </si>
-  <si>
-    <t>327-856-018</t>
-  </si>
-  <si>
-    <t>092505957638</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Carlito</t>
-  </si>
-  <si>
-    <t>Mendoza</t>
-  </si>
-  <si>
-    <t>Lindog</t>
-  </si>
-  <si>
-    <t>Zenaida</t>
-  </si>
-  <si>
-    <t>G.B Lontok Memorial School</t>
-  </si>
-  <si>
-    <t>Lipa City National High School</t>
-  </si>
-  <si>
-    <t>University of Batangas</t>
-  </si>
-  <si>
-    <t>Bachelor of Science</t>
-  </si>
-  <si>
-    <t>Ms. Mayling Ilagan-Capuno</t>
-  </si>
-  <si>
-    <t>University of Batangas- Lipa Campus</t>
-  </si>
-  <si>
-    <t>Ms. Kielly Chrizza MaeTojino</t>
-  </si>
-  <si>
-    <t>Philippine Airlines</t>
-  </si>
-  <si>
-    <t>Mr. John Tech</t>
-  </si>
-  <si>
-    <t>Straive (SPi Global)</t>
-  </si>
-  <si>
-    <t>Content Editor</t>
-  </si>
-  <si>
-    <t>Aruze Global Shared Services</t>
-  </si>
-  <si>
-    <t>Graphic Artist</t>
-  </si>
-  <si>
-    <t>Junior Software Developer</t>
-  </si>
-  <si>
-    <t>Sysplex IT Solution OPC</t>
-  </si>
-  <si>
-    <t>06/23/2023</t>
-  </si>
-  <si>
-    <t>08/15/2025</t>
-  </si>
-  <si>
-    <t>System Developer</t>
-  </si>
-  <si>
-    <t>Asia Cargo Container Inc.</t>
-  </si>
-  <si>
-    <t>08/27/2025</t>
-  </si>
-  <si>
-    <t>01/31/2026</t>
-  </si>
-  <si>
-    <t>MERN Stack Developer</t>
-  </si>
-  <si>
-    <t>06/15/2023</t>
-  </si>
-  <si>
-    <t>06/19/2023</t>
-  </si>
-  <si>
     <t>Playing mobile legend</t>
-  </si>
-  <si>
-    <t>May 8, 2026</t>
-  </si>
-  <si>
-    <t>Christopher Avenido</t>
   </si>
 </sst>
 </file>
@@ -3659,29 +3539,365 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3699,36 +3915,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -3738,345 +3946,154 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4090,57 +4107,357 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4150,12 +4467,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4172,28 +4483,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -4231,18 +4528,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4253,10 +4538,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4272,441 +4553,134 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4715,6 +4689,36 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4738,162 +4742,106 @@
     <xf numFmtId="49" fontId="41" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4907,12 +4855,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4923,59 +4865,19 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4983,6 +4885,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5041,79 +4946,54 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5226,7 +5106,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5234,7 +5114,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5242,7 +5122,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5254,7 +5134,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5262,7 +5142,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5270,7 +5150,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5278,7 +5158,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5298,15 +5178,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5318,7 +5198,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5326,7 +5206,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10263,20 +10143,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="524"/>
-      <c r="B1" s="525"/>
-      <c r="C1" s="525"/>
-      <c r="D1" s="525"/>
-      <c r="E1" s="525"/>
-      <c r="F1" s="525"/>
-      <c r="G1" s="525"/>
-      <c r="H1" s="525"/>
-      <c r="I1" s="525"/>
-      <c r="J1" s="525"/>
-      <c r="K1" s="525"/>
-      <c r="L1" s="525"/>
-      <c r="M1" s="525"/>
-      <c r="N1" s="526"/>
+      <c r="A1" s="503"/>
+      <c r="B1" s="504"/>
+      <c r="C1" s="504"/>
+      <c r="D1" s="504"/>
+      <c r="E1" s="504"/>
+      <c r="F1" s="504"/>
+      <c r="G1" s="504"/>
+      <c r="H1" s="504"/>
+      <c r="I1" s="504"/>
+      <c r="J1" s="504"/>
+      <c r="K1" s="504"/>
+      <c r="L1" s="504"/>
+      <c r="M1" s="504"/>
+      <c r="N1" s="505"/>
     </row>
     <row r="2" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="169"/>
@@ -10306,58 +10186,58 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="527" t="s">
+      <c r="A3" s="506" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="528"/>
-      <c r="C3" s="528"/>
-      <c r="D3" s="528"/>
-      <c r="E3" s="528"/>
-      <c r="F3" s="528"/>
-      <c r="G3" s="528"/>
-      <c r="H3" s="528"/>
-      <c r="I3" s="528"/>
-      <c r="J3" s="528"/>
-      <c r="K3" s="528"/>
-      <c r="L3" s="528"/>
-      <c r="M3" s="528"/>
-      <c r="N3" s="529"/>
+      <c r="B3" s="507"/>
+      <c r="C3" s="507"/>
+      <c r="D3" s="507"/>
+      <c r="E3" s="507"/>
+      <c r="F3" s="507"/>
+      <c r="G3" s="507"/>
+      <c r="H3" s="507"/>
+      <c r="I3" s="507"/>
+      <c r="J3" s="507"/>
+      <c r="K3" s="507"/>
+      <c r="L3" s="507"/>
+      <c r="M3" s="507"/>
+      <c r="N3" s="508"/>
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="557" t="s">
+      <c r="A4" s="537" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="558"/>
-      <c r="C4" s="558"/>
-      <c r="D4" s="558"/>
-      <c r="E4" s="558"/>
-      <c r="F4" s="558"/>
-      <c r="G4" s="558"/>
-      <c r="H4" s="558"/>
-      <c r="I4" s="558"/>
-      <c r="J4" s="558"/>
-      <c r="K4" s="558"/>
-      <c r="L4" s="558"/>
-      <c r="M4" s="558"/>
-      <c r="N4" s="559"/>
+      <c r="B4" s="538"/>
+      <c r="C4" s="538"/>
+      <c r="D4" s="538"/>
+      <c r="E4" s="538"/>
+      <c r="F4" s="538"/>
+      <c r="G4" s="538"/>
+      <c r="H4" s="538"/>
+      <c r="I4" s="538"/>
+      <c r="J4" s="538"/>
+      <c r="K4" s="538"/>
+      <c r="L4" s="538"/>
+      <c r="M4" s="538"/>
+      <c r="N4" s="539"/>
     </row>
     <row r="5" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="441" t="s">
+      <c r="A5" s="578" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="442"/>
-      <c r="C5" s="442"/>
-      <c r="D5" s="442"/>
-      <c r="E5" s="442"/>
-      <c r="F5" s="442"/>
-      <c r="G5" s="442"/>
-      <c r="H5" s="442"/>
-      <c r="I5" s="442"/>
-      <c r="J5" s="442"/>
-      <c r="K5" s="442"/>
-      <c r="L5" s="442"/>
-      <c r="M5" s="442"/>
-      <c r="N5" s="443"/>
+      <c r="B5" s="579"/>
+      <c r="C5" s="579"/>
+      <c r="D5" s="579"/>
+      <c r="E5" s="579"/>
+      <c r="F5" s="579"/>
+      <c r="G5" s="579"/>
+      <c r="H5" s="579"/>
+      <c r="I5" s="579"/>
+      <c r="J5" s="579"/>
+      <c r="K5" s="579"/>
+      <c r="L5" s="579"/>
+      <c r="M5" s="579"/>
+      <c r="N5" s="580"/>
     </row>
     <row r="6" spans="1:18" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A6" s="205"/>
@@ -10394,42 +10274,42 @@
       <c r="N8" s="164"/>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="530" t="s">
+      <c r="A9" s="509" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="531"/>
-      <c r="C9" s="531"/>
-      <c r="D9" s="531"/>
-      <c r="E9" s="531"/>
-      <c r="F9" s="531"/>
-      <c r="G9" s="531"/>
-      <c r="H9" s="531"/>
-      <c r="I9" s="531"/>
-      <c r="J9" s="531"/>
-      <c r="K9" s="531"/>
-      <c r="L9" s="531"/>
-      <c r="M9" s="531"/>
-      <c r="N9" s="532"/>
+      <c r="B9" s="510"/>
+      <c r="C9" s="510"/>
+      <c r="D9" s="510"/>
+      <c r="E9" s="510"/>
+      <c r="F9" s="510"/>
+      <c r="G9" s="510"/>
+      <c r="H9" s="510"/>
+      <c r="I9" s="510"/>
+      <c r="J9" s="510"/>
+      <c r="K9" s="510"/>
+      <c r="L9" s="510"/>
+      <c r="M9" s="510"/>
+      <c r="N9" s="511"/>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="547" t="s">
+      <c r="B10" s="527" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="483"/>
-      <c r="D10" s="539"/>
-      <c r="E10" s="539"/>
-      <c r="F10" s="539"/>
-      <c r="G10" s="539"/>
-      <c r="H10" s="539"/>
-      <c r="I10" s="539"/>
-      <c r="J10" s="539"/>
-      <c r="K10" s="539"/>
-      <c r="L10" s="539"/>
-      <c r="M10" s="539"/>
-      <c r="N10" s="540"/>
+      <c r="C10" s="528"/>
+      <c r="D10" s="518"/>
+      <c r="E10" s="518"/>
+      <c r="F10" s="518"/>
+      <c r="G10" s="518"/>
+      <c r="H10" s="518"/>
+      <c r="I10" s="518"/>
+      <c r="J10" s="518"/>
+      <c r="K10" s="518"/>
+      <c r="L10" s="518"/>
+      <c r="M10" s="518"/>
+      <c r="N10" s="519"/>
       <c r="P10" s="96" t="s">
         <v>11</v>
       </c>
@@ -10438,10 +10318,10 @@
       <c r="A11" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="548" t="s">
+      <c r="B11" s="529" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="549"/>
+      <c r="C11" s="530"/>
       <c r="D11" s="213"/>
       <c r="E11" s="214"/>
       <c r="F11" s="214"/>
@@ -10450,11 +10330,11 @@
       <c r="I11" s="214"/>
       <c r="J11" s="214"/>
       <c r="K11" s="214"/>
-      <c r="L11" s="484" t="s">
+      <c r="L11" s="549" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="485"/>
-      <c r="N11" s="486"/>
+      <c r="M11" s="550"/>
+      <c r="N11" s="551"/>
       <c r="P11" s="97" t="s">
         <v>15</v>
       </c>
@@ -10464,10 +10344,10 @@
     </row>
     <row r="12" spans="1:18" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="175"/>
-      <c r="B12" s="550" t="s">
+      <c r="B12" s="531" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="551"/>
+      <c r="C12" s="532"/>
       <c r="D12" s="210"/>
       <c r="E12" s="211"/>
       <c r="F12" s="211"/>
@@ -10490,23 +10370,23 @@
       <c r="A13" s="250" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="482" t="s">
+      <c r="B13" s="609" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="483"/>
-      <c r="D13" s="487"/>
-      <c r="E13" s="487"/>
-      <c r="F13" s="488"/>
+      <c r="C13" s="528"/>
+      <c r="D13" s="552"/>
+      <c r="E13" s="552"/>
+      <c r="F13" s="553"/>
       <c r="G13" s="103" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="148"/>
       <c r="I13" s="148"/>
-      <c r="J13" s="494"/>
-      <c r="K13" s="495"/>
-      <c r="L13" s="495"/>
-      <c r="M13" s="495"/>
-      <c r="N13" s="496"/>
+      <c r="J13" s="559"/>
+      <c r="K13" s="560"/>
+      <c r="L13" s="560"/>
+      <c r="M13" s="560"/>
+      <c r="N13" s="561"/>
       <c r="P13" s="97" t="s">
         <v>23</v>
       </c>
@@ -10540,21 +10420,21 @@
         <v>26</v>
       </c>
       <c r="C15" s="98"/>
-      <c r="D15" s="511"/>
-      <c r="E15" s="511"/>
-      <c r="F15" s="512"/>
-      <c r="G15" s="492" t="s">
+      <c r="D15" s="573"/>
+      <c r="E15" s="573"/>
+      <c r="F15" s="574"/>
+      <c r="G15" s="557" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="493"/>
-      <c r="I15" s="493"/>
+      <c r="H15" s="558"/>
+      <c r="I15" s="558"/>
       <c r="J15" s="149"/>
       <c r="K15" s="150"/>
-      <c r="L15" s="497" t="s">
+      <c r="L15" s="563" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="497"/>
-      <c r="N15" s="498"/>
+      <c r="M15" s="563"/>
+      <c r="N15" s="564"/>
       <c r="P15" s="97" t="s">
         <v>29</v>
       </c>
@@ -10570,14 +10450,14 @@
         <v>32</v>
       </c>
       <c r="C16" s="99"/>
-      <c r="D16" s="541"/>
-      <c r="E16" s="541"/>
-      <c r="F16" s="542"/>
-      <c r="G16" s="489" t="s">
+      <c r="D16" s="520"/>
+      <c r="E16" s="520"/>
+      <c r="F16" s="521"/>
+      <c r="G16" s="554" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="490"/>
-      <c r="I16" s="491"/>
+      <c r="H16" s="555"/>
+      <c r="I16" s="556"/>
       <c r="N16" s="164"/>
       <c r="P16" s="97" t="s">
         <v>34</v>
@@ -10587,49 +10467,49 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="465">
+      <c r="A17" s="596">
         <v>6</v>
       </c>
-      <c r="B17" s="478" t="s">
+      <c r="B17" s="605" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="479"/>
-      <c r="D17" s="476"/>
-      <c r="E17" s="476"/>
-      <c r="F17" s="476"/>
+      <c r="C17" s="606"/>
+      <c r="D17" s="604"/>
+      <c r="E17" s="604"/>
+      <c r="F17" s="604"/>
       <c r="G17" s="104" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="105"/>
-      <c r="I17" s="507"/>
-      <c r="J17" s="499"/>
-      <c r="K17" s="499"/>
-      <c r="L17" s="499"/>
-      <c r="M17" s="499"/>
-      <c r="N17" s="500"/>
+      <c r="I17" s="484"/>
+      <c r="J17" s="485"/>
+      <c r="K17" s="485"/>
+      <c r="L17" s="485"/>
+      <c r="M17" s="485"/>
+      <c r="N17" s="486"/>
       <c r="Q17" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="466"/>
-      <c r="B18" s="480"/>
-      <c r="C18" s="481"/>
-      <c r="D18" s="477"/>
-      <c r="E18" s="477"/>
-      <c r="F18" s="477"/>
+      <c r="A18" s="597"/>
+      <c r="B18" s="607"/>
+      <c r="C18" s="608"/>
+      <c r="D18" s="525"/>
+      <c r="E18" s="525"/>
+      <c r="F18" s="525"/>
       <c r="G18" s="157"/>
       <c r="H18" s="106"/>
-      <c r="I18" s="502" t="s">
+      <c r="I18" s="566" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="444"/>
-      <c r="K18" s="444"/>
-      <c r="L18" s="444" t="s">
+      <c r="J18" s="567"/>
+      <c r="K18" s="567"/>
+      <c r="L18" s="567" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="444"/>
-      <c r="N18" s="445"/>
+      <c r="M18" s="567"/>
+      <c r="N18" s="568"/>
       <c r="Q18" s="3" t="s">
         <v>41</v>
       </c>
@@ -10643,100 +10523,100 @@
       <c r="F19" s="165"/>
       <c r="G19" s="157"/>
       <c r="H19" s="106"/>
-      <c r="I19" s="446"/>
-      <c r="J19" s="447"/>
-      <c r="K19" s="447"/>
-      <c r="L19" s="450"/>
-      <c r="M19" s="447"/>
-      <c r="N19" s="451"/>
+      <c r="I19" s="581"/>
+      <c r="J19" s="582"/>
+      <c r="K19" s="582"/>
+      <c r="L19" s="585"/>
+      <c r="M19" s="582"/>
+      <c r="N19" s="586"/>
       <c r="Q19" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="466"/>
+      <c r="A20" s="597"/>
       <c r="B20" s="229"/>
       <c r="C20" s="140"/>
       <c r="D20" s="141"/>
-      <c r="E20" s="477"/>
-      <c r="F20" s="477"/>
+      <c r="E20" s="525"/>
+      <c r="F20" s="525"/>
       <c r="G20" s="155"/>
       <c r="H20" s="163"/>
-      <c r="I20" s="448"/>
-      <c r="J20" s="449"/>
-      <c r="K20" s="449"/>
-      <c r="L20" s="449"/>
-      <c r="M20" s="449"/>
-      <c r="N20" s="452"/>
+      <c r="I20" s="583"/>
+      <c r="J20" s="584"/>
+      <c r="K20" s="584"/>
+      <c r="L20" s="584"/>
+      <c r="M20" s="584"/>
+      <c r="N20" s="587"/>
       <c r="Q20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="467"/>
+      <c r="A21" s="598"/>
       <c r="B21" s="230"/>
       <c r="C21" s="138"/>
       <c r="D21" s="142"/>
-      <c r="E21" s="546"/>
-      <c r="F21" s="546"/>
+      <c r="E21" s="526"/>
+      <c r="F21" s="526"/>
       <c r="G21" s="155"/>
       <c r="H21" s="163"/>
-      <c r="I21" s="453" t="s">
+      <c r="I21" s="588" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="454"/>
-      <c r="K21" s="454"/>
-      <c r="L21" s="580" t="s">
+      <c r="J21" s="589"/>
+      <c r="K21" s="589"/>
+      <c r="L21" s="481" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="581"/>
-      <c r="N21" s="582"/>
+      <c r="M21" s="482"/>
+      <c r="N21" s="483"/>
       <c r="Q21" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="474" t="s">
+      <c r="A22" s="602" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="544" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="440"/>
-      <c r="D22" s="518"/>
-      <c r="E22" s="518"/>
-      <c r="F22" s="518"/>
+      <c r="C22" s="545"/>
+      <c r="D22" s="540"/>
+      <c r="E22" s="540"/>
+      <c r="F22" s="540"/>
       <c r="G22" s="155"/>
       <c r="H22" s="163"/>
-      <c r="I22" s="507"/>
-      <c r="J22" s="499"/>
-      <c r="K22" s="499"/>
-      <c r="L22" s="499"/>
-      <c r="M22" s="499"/>
-      <c r="N22" s="500"/>
+      <c r="I22" s="484"/>
+      <c r="J22" s="485"/>
+      <c r="K22" s="485"/>
+      <c r="L22" s="485"/>
+      <c r="M22" s="485"/>
+      <c r="N22" s="486"/>
       <c r="Q22" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="475"/>
-      <c r="B23" s="519"/>
-      <c r="C23" s="520"/>
-      <c r="D23" s="458"/>
-      <c r="E23" s="458"/>
-      <c r="F23" s="458"/>
+      <c r="A23" s="603"/>
+      <c r="B23" s="546"/>
+      <c r="C23" s="547"/>
+      <c r="D23" s="541"/>
+      <c r="E23" s="541"/>
+      <c r="F23" s="541"/>
       <c r="G23" s="155"/>
       <c r="H23" s="163"/>
-      <c r="I23" s="585" t="s">
+      <c r="I23" s="489" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="586"/>
-      <c r="K23" s="586"/>
-      <c r="L23" s="583" t="s">
+      <c r="J23" s="490"/>
+      <c r="K23" s="490"/>
+      <c r="L23" s="487" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="583"/>
-      <c r="N23" s="584"/>
+      <c r="M23" s="487"/>
+      <c r="N23" s="488"/>
       <c r="Q23" s="3" t="s">
         <v>52</v>
       </c>
@@ -10745,167 +10625,163 @@
       <c r="A24" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="521" t="s">
+      <c r="B24" s="534" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="522"/>
-      <c r="D24" s="501"/>
-      <c r="E24" s="501"/>
-      <c r="F24" s="501"/>
-      <c r="G24" s="552" t="s">
+      <c r="C24" s="535"/>
+      <c r="D24" s="565"/>
+      <c r="E24" s="565"/>
+      <c r="F24" s="565"/>
+      <c r="G24" s="496" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="553"/>
-      <c r="I24" s="508"/>
-      <c r="J24" s="509"/>
-      <c r="K24" s="509"/>
-      <c r="L24" s="509"/>
-      <c r="M24" s="509"/>
-      <c r="N24" s="510"/>
+      <c r="H24" s="474"/>
+      <c r="I24" s="497"/>
+      <c r="J24" s="498"/>
+      <c r="K24" s="498"/>
+      <c r="L24" s="498"/>
+      <c r="M24" s="498"/>
+      <c r="N24" s="499"/>
       <c r="Q24" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="455" t="s">
+      <c r="A25" s="542" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="439" t="s">
+      <c r="B25" s="544" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="440"/>
-      <c r="D25" s="457"/>
-      <c r="E25" s="457"/>
-      <c r="F25" s="457"/>
+      <c r="C25" s="545"/>
+      <c r="D25" s="590"/>
+      <c r="E25" s="590"/>
+      <c r="F25" s="590"/>
       <c r="G25" s="111" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="100"/>
-      <c r="I25" s="513"/>
-      <c r="J25" s="514"/>
-      <c r="K25" s="514"/>
-      <c r="L25" s="514"/>
-      <c r="M25" s="514"/>
-      <c r="N25" s="590"/>
+      <c r="I25" s="500"/>
+      <c r="J25" s="494"/>
+      <c r="K25" s="494"/>
+      <c r="L25" s="494"/>
+      <c r="M25" s="494"/>
+      <c r="N25" s="495"/>
       <c r="Q25" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="456"/>
-      <c r="B26" s="519"/>
-      <c r="C26" s="520"/>
-      <c r="D26" s="458"/>
-      <c r="E26" s="458"/>
-      <c r="F26" s="458"/>
+      <c r="A26" s="543"/>
+      <c r="B26" s="546"/>
+      <c r="C26" s="547"/>
+      <c r="D26" s="541"/>
+      <c r="E26" s="541"/>
+      <c r="F26" s="541"/>
       <c r="G26" s="155"/>
       <c r="H26" s="163"/>
-      <c r="I26" s="502" t="s">
+      <c r="I26" s="566" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="444"/>
-      <c r="K26" s="444"/>
-      <c r="L26" s="444" t="s">
+      <c r="J26" s="567"/>
+      <c r="K26" s="567"/>
+      <c r="L26" s="567" t="s">
         <v>40</v>
       </c>
-      <c r="M26" s="444"/>
-      <c r="N26" s="445"/>
+      <c r="M26" s="567"/>
+      <c r="N26" s="568"/>
       <c r="Q26" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="455" t="s">
+      <c r="A27" s="542" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="523" t="s">
+      <c r="B27" s="548" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="440"/>
-      <c r="D27" s="457"/>
-      <c r="E27" s="457"/>
-      <c r="F27" s="457"/>
+      <c r="C27" s="545"/>
+      <c r="D27" s="590"/>
+      <c r="E27" s="590"/>
+      <c r="F27" s="590"/>
       <c r="G27" s="157"/>
       <c r="H27" s="106"/>
-      <c r="I27" s="513"/>
-      <c r="J27" s="514"/>
-      <c r="K27" s="514"/>
-      <c r="L27" s="514"/>
-      <c r="M27" s="514"/>
-      <c r="N27" s="590"/>
+      <c r="I27" s="500"/>
+      <c r="J27" s="494"/>
+      <c r="K27" s="494"/>
+      <c r="L27" s="494"/>
+      <c r="M27" s="494"/>
+      <c r="N27" s="495"/>
       <c r="Q27" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="456"/>
-      <c r="B28" s="519"/>
-      <c r="C28" s="520"/>
-      <c r="D28" s="458"/>
-      <c r="E28" s="458"/>
-      <c r="F28" s="458"/>
+      <c r="A28" s="543"/>
+      <c r="B28" s="546"/>
+      <c r="C28" s="547"/>
+      <c r="D28" s="541"/>
+      <c r="E28" s="541"/>
+      <c r="F28" s="541"/>
       <c r="G28" s="157"/>
       <c r="H28" s="106"/>
-      <c r="I28" s="503" t="s">
+      <c r="I28" s="569" t="s">
         <v>44</v>
       </c>
-      <c r="J28" s="504"/>
-      <c r="K28" s="504"/>
-      <c r="L28" s="505" t="s">
+      <c r="J28" s="570"/>
+      <c r="K28" s="570"/>
+      <c r="L28" s="571" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="504"/>
-      <c r="N28" s="506"/>
+      <c r="M28" s="570"/>
+      <c r="N28" s="572"/>
       <c r="Q28" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="455" t="s">
+      <c r="A29" s="542" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="439" t="s">
+      <c r="B29" s="544" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="440"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="545"/>
+      <c r="D29" s="591"/>
+      <c r="E29" s="562"/>
+      <c r="F29" s="592"/>
       <c r="G29" s="157"/>
       <c r="H29" s="167"/>
       <c r="I29" s="159"/>
-      <c r="J29" s="281" t="s">
-        <v>406</v>
-      </c>
+      <c r="J29" s="281"/>
       <c r="K29" s="160"/>
       <c r="L29" s="160"/>
-      <c r="M29" s="281" t="s">
-        <v>405</v>
-      </c>
+      <c r="M29" s="281"/>
       <c r="N29" s="179"/>
       <c r="Q29" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="456"/>
-      <c r="B30" s="519"/>
-      <c r="C30" s="520"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="464"/>
+      <c r="A30" s="543"/>
+      <c r="B30" s="546"/>
+      <c r="C30" s="547"/>
+      <c r="D30" s="593"/>
+      <c r="E30" s="594"/>
+      <c r="F30" s="595"/>
       <c r="G30" s="157"/>
       <c r="H30" s="167"/>
-      <c r="I30" s="587" t="s">
+      <c r="I30" s="491" t="s">
         <v>50</v>
       </c>
-      <c r="J30" s="587"/>
-      <c r="K30" s="587"/>
-      <c r="L30" s="587" t="s">
+      <c r="J30" s="491"/>
+      <c r="K30" s="491"/>
+      <c r="L30" s="491" t="s">
         <v>51</v>
       </c>
-      <c r="M30" s="587"/>
-      <c r="N30" s="588"/>
+      <c r="M30" s="491"/>
+      <c r="N30" s="492"/>
       <c r="Q30" s="3" t="s">
         <v>69</v>
       </c>
@@ -10918,23 +10794,19 @@
         <v>71</v>
       </c>
       <c r="C31" s="99"/>
-      <c r="D31" s="460" t="s">
-        <v>411</v>
-      </c>
-      <c r="E31" s="460"/>
-      <c r="F31" s="460"/>
-      <c r="G31" s="552" t="s">
+      <c r="D31" s="562"/>
+      <c r="E31" s="562"/>
+      <c r="F31" s="562"/>
+      <c r="G31" s="496" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="553"/>
-      <c r="I31" s="585" t="s">
-        <v>407</v>
-      </c>
-      <c r="J31" s="586"/>
-      <c r="K31" s="586"/>
-      <c r="L31" s="580"/>
-      <c r="M31" s="580"/>
-      <c r="N31" s="589"/>
+      <c r="H31" s="474"/>
+      <c r="I31" s="489"/>
+      <c r="J31" s="490"/>
+      <c r="K31" s="490"/>
+      <c r="L31" s="481"/>
+      <c r="M31" s="481"/>
+      <c r="N31" s="493"/>
       <c r="Q31" s="3" t="s">
         <v>72</v>
       </c>
@@ -10947,48 +10819,42 @@
         <v>74</v>
       </c>
       <c r="C32" s="99"/>
-      <c r="D32" s="501"/>
-      <c r="E32" s="501"/>
-      <c r="F32" s="501"/>
+      <c r="D32" s="565"/>
+      <c r="E32" s="565"/>
+      <c r="F32" s="565"/>
       <c r="G32" s="154" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="158"/>
-      <c r="I32" s="508" t="s">
-        <v>408</v>
-      </c>
-      <c r="J32" s="509"/>
-      <c r="K32" s="509"/>
-      <c r="L32" s="509"/>
-      <c r="M32" s="509"/>
-      <c r="N32" s="510"/>
+      <c r="I32" s="497"/>
+      <c r="J32" s="498"/>
+      <c r="K32" s="498"/>
+      <c r="L32" s="498"/>
+      <c r="M32" s="498"/>
+      <c r="N32" s="499"/>
       <c r="Q32" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="555" t="s">
+      <c r="A33" s="533" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="521"/>
-      <c r="C33" s="522"/>
-      <c r="D33" s="556" t="s">
-        <v>410</v>
-      </c>
-      <c r="E33" s="556"/>
-      <c r="F33" s="556"/>
+      <c r="B33" s="534"/>
+      <c r="C33" s="535"/>
+      <c r="D33" s="536"/>
+      <c r="E33" s="536"/>
+      <c r="F33" s="536"/>
       <c r="G33" s="212" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="156"/>
-      <c r="I33" s="508" t="s">
-        <v>408</v>
-      </c>
-      <c r="J33" s="509"/>
-      <c r="K33" s="509"/>
-      <c r="L33" s="509"/>
-      <c r="M33" s="509"/>
-      <c r="N33" s="510"/>
+      <c r="I33" s="497"/>
+      <c r="J33" s="498"/>
+      <c r="K33" s="498"/>
+      <c r="L33" s="498"/>
+      <c r="M33" s="498"/>
+      <c r="N33" s="499"/>
       <c r="Q33" s="3" t="s">
         <v>79</v>
       </c>
@@ -10999,21 +10865,19 @@
       </c>
       <c r="B34" s="231"/>
       <c r="C34" s="161"/>
-      <c r="D34" s="545"/>
-      <c r="E34" s="545"/>
-      <c r="F34" s="545"/>
+      <c r="D34" s="524"/>
+      <c r="E34" s="524"/>
+      <c r="F34" s="524"/>
       <c r="G34" s="111" t="s">
         <v>81</v>
       </c>
       <c r="H34" s="100"/>
-      <c r="I34" s="515" t="s">
-        <v>409</v>
-      </c>
-      <c r="J34" s="516"/>
-      <c r="K34" s="516"/>
-      <c r="L34" s="516"/>
-      <c r="M34" s="516"/>
-      <c r="N34" s="517"/>
+      <c r="I34" s="575"/>
+      <c r="J34" s="576"/>
+      <c r="K34" s="576"/>
+      <c r="L34" s="576"/>
+      <c r="M34" s="576"/>
+      <c r="N34" s="577"/>
       <c r="Q34" s="3" t="s">
         <v>82</v>
       </c>
@@ -11047,23 +10911,21 @@
         <v>86</v>
       </c>
       <c r="C36" s="236"/>
-      <c r="D36" s="468" t="s">
-        <v>412</v>
-      </c>
-      <c r="E36" s="469"/>
-      <c r="F36" s="469"/>
-      <c r="G36" s="469"/>
-      <c r="H36" s="470"/>
-      <c r="I36" s="591" t="s">
+      <c r="D36" s="599"/>
+      <c r="E36" s="600"/>
+      <c r="F36" s="600"/>
+      <c r="G36" s="600"/>
+      <c r="H36" s="601"/>
+      <c r="I36" s="501" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="591"/>
-      <c r="K36" s="591"/>
-      <c r="L36" s="592"/>
-      <c r="M36" s="344" t="s">
+      <c r="J36" s="501"/>
+      <c r="K36" s="501"/>
+      <c r="L36" s="502"/>
+      <c r="M36" s="375" t="s">
         <v>88</v>
       </c>
-      <c r="N36" s="346"/>
+      <c r="N36" s="377"/>
       <c r="Q36" s="3" t="s">
         <v>89</v>
       </c>
@@ -11074,17 +10936,17 @@
         <v>90</v>
       </c>
       <c r="C37" s="167"/>
-      <c r="D37" s="471"/>
-      <c r="E37" s="472"/>
-      <c r="F37" s="473"/>
-      <c r="G37" s="554" t="s">
+      <c r="D37" s="437"/>
+      <c r="E37" s="438"/>
+      <c r="F37" s="439"/>
+      <c r="G37" s="453" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="554"/>
-      <c r="I37" s="426"/>
-      <c r="J37" s="426"/>
-      <c r="K37" s="426"/>
-      <c r="L37" s="427"/>
+      <c r="H37" s="453"/>
+      <c r="I37" s="435"/>
+      <c r="J37" s="435"/>
+      <c r="K37" s="435"/>
+      <c r="L37" s="436"/>
       <c r="M37" s="433"/>
       <c r="N37" s="434"/>
       <c r="Q37" s="3" t="s">
@@ -11097,15 +10959,15 @@
         <v>93</v>
       </c>
       <c r="C38" s="226"/>
-      <c r="D38" s="471"/>
-      <c r="E38" s="472"/>
-      <c r="F38" s="472"/>
-      <c r="G38" s="472"/>
-      <c r="H38" s="473"/>
-      <c r="I38" s="426"/>
-      <c r="J38" s="426"/>
-      <c r="K38" s="426"/>
-      <c r="L38" s="427"/>
+      <c r="D38" s="437"/>
+      <c r="E38" s="438"/>
+      <c r="F38" s="438"/>
+      <c r="G38" s="438"/>
+      <c r="H38" s="439"/>
+      <c r="I38" s="435"/>
+      <c r="J38" s="435"/>
+      <c r="K38" s="435"/>
+      <c r="L38" s="436"/>
       <c r="M38" s="433"/>
       <c r="N38" s="434"/>
       <c r="Q38" s="3" t="s">
@@ -11118,15 +10980,15 @@
         <v>95</v>
       </c>
       <c r="C39" s="99"/>
-      <c r="D39" s="471"/>
-      <c r="E39" s="472"/>
-      <c r="F39" s="472"/>
-      <c r="G39" s="472"/>
-      <c r="H39" s="473"/>
-      <c r="I39" s="426"/>
-      <c r="J39" s="426"/>
-      <c r="K39" s="426"/>
-      <c r="L39" s="427"/>
+      <c r="D39" s="437"/>
+      <c r="E39" s="438"/>
+      <c r="F39" s="438"/>
+      <c r="G39" s="438"/>
+      <c r="H39" s="439"/>
+      <c r="I39" s="435"/>
+      <c r="J39" s="435"/>
+      <c r="K39" s="435"/>
+      <c r="L39" s="436"/>
       <c r="M39" s="433"/>
       <c r="N39" s="434"/>
       <c r="Q39" s="3" t="s">
@@ -11139,15 +11001,15 @@
         <v>97</v>
       </c>
       <c r="C40" s="99"/>
-      <c r="D40" s="471"/>
-      <c r="E40" s="472"/>
-      <c r="F40" s="472"/>
-      <c r="G40" s="472"/>
-      <c r="H40" s="473"/>
-      <c r="I40" s="426"/>
-      <c r="J40" s="426"/>
-      <c r="K40" s="426"/>
-      <c r="L40" s="427"/>
+      <c r="D40" s="437"/>
+      <c r="E40" s="438"/>
+      <c r="F40" s="438"/>
+      <c r="G40" s="438"/>
+      <c r="H40" s="439"/>
+      <c r="I40" s="435"/>
+      <c r="J40" s="435"/>
+      <c r="K40" s="435"/>
+      <c r="L40" s="436"/>
       <c r="M40" s="433"/>
       <c r="N40" s="434"/>
       <c r="Q40" s="3" t="s">
@@ -11160,15 +11022,15 @@
         <v>99</v>
       </c>
       <c r="C41" s="99"/>
-      <c r="D41" s="471"/>
-      <c r="E41" s="472"/>
-      <c r="F41" s="472"/>
-      <c r="G41" s="472"/>
-      <c r="H41" s="473"/>
-      <c r="I41" s="426"/>
-      <c r="J41" s="426"/>
-      <c r="K41" s="426"/>
-      <c r="L41" s="427"/>
+      <c r="D41" s="437"/>
+      <c r="E41" s="438"/>
+      <c r="F41" s="438"/>
+      <c r="G41" s="438"/>
+      <c r="H41" s="439"/>
+      <c r="I41" s="435"/>
+      <c r="J41" s="435"/>
+      <c r="K41" s="435"/>
+      <c r="L41" s="436"/>
       <c r="M41" s="433"/>
       <c r="N41" s="434"/>
       <c r="Q41" s="3" t="s">
@@ -11181,15 +11043,15 @@
         <v>101</v>
       </c>
       <c r="C42" s="139"/>
-      <c r="D42" s="471"/>
-      <c r="E42" s="472"/>
-      <c r="F42" s="472"/>
-      <c r="G42" s="472"/>
-      <c r="H42" s="473"/>
-      <c r="I42" s="426"/>
-      <c r="J42" s="426"/>
-      <c r="K42" s="426"/>
-      <c r="L42" s="427"/>
+      <c r="D42" s="437"/>
+      <c r="E42" s="438"/>
+      <c r="F42" s="438"/>
+      <c r="G42" s="438"/>
+      <c r="H42" s="439"/>
+      <c r="I42" s="435"/>
+      <c r="J42" s="435"/>
+      <c r="K42" s="435"/>
+      <c r="L42" s="436"/>
       <c r="M42" s="433"/>
       <c r="N42" s="434"/>
       <c r="Q42" s="3" t="s">
@@ -11204,17 +11066,15 @@
         <v>104</v>
       </c>
       <c r="C43" s="105"/>
-      <c r="D43" s="471" t="s">
-        <v>403</v>
-      </c>
-      <c r="E43" s="472"/>
-      <c r="F43" s="472"/>
-      <c r="G43" s="472"/>
-      <c r="H43" s="473"/>
-      <c r="I43" s="426"/>
-      <c r="J43" s="426"/>
-      <c r="K43" s="426"/>
-      <c r="L43" s="427"/>
+      <c r="D43" s="437"/>
+      <c r="E43" s="438"/>
+      <c r="F43" s="438"/>
+      <c r="G43" s="438"/>
+      <c r="H43" s="439"/>
+      <c r="I43" s="435"/>
+      <c r="J43" s="435"/>
+      <c r="K43" s="435"/>
+      <c r="L43" s="436"/>
       <c r="M43" s="433"/>
       <c r="N43" s="434"/>
       <c r="Q43" s="3" t="s">
@@ -11227,19 +11087,17 @@
         <v>13</v>
       </c>
       <c r="C44" s="163"/>
-      <c r="D44" s="471" t="s">
-        <v>413</v>
-      </c>
-      <c r="E44" s="472"/>
-      <c r="F44" s="473"/>
-      <c r="G44" s="554" t="s">
+      <c r="D44" s="437"/>
+      <c r="E44" s="438"/>
+      <c r="F44" s="439"/>
+      <c r="G44" s="453" t="s">
         <v>106</v>
       </c>
-      <c r="H44" s="554"/>
-      <c r="I44" s="426"/>
-      <c r="J44" s="426"/>
-      <c r="K44" s="426"/>
-      <c r="L44" s="427"/>
+      <c r="H44" s="453"/>
+      <c r="I44" s="435"/>
+      <c r="J44" s="435"/>
+      <c r="K44" s="435"/>
+      <c r="L44" s="436"/>
       <c r="M44" s="433"/>
       <c r="N44" s="434"/>
       <c r="Q44" s="3" t="s">
@@ -11252,17 +11110,15 @@
         <v>17</v>
       </c>
       <c r="C45" s="219"/>
-      <c r="D45" s="471" t="s">
-        <v>414</v>
-      </c>
-      <c r="E45" s="472"/>
-      <c r="F45" s="472"/>
-      <c r="G45" s="472"/>
-      <c r="H45" s="473"/>
-      <c r="I45" s="426"/>
-      <c r="J45" s="426"/>
-      <c r="K45" s="426"/>
-      <c r="L45" s="427"/>
+      <c r="D45" s="437"/>
+      <c r="E45" s="438"/>
+      <c r="F45" s="438"/>
+      <c r="G45" s="438"/>
+      <c r="H45" s="439"/>
+      <c r="I45" s="435"/>
+      <c r="J45" s="435"/>
+      <c r="K45" s="435"/>
+      <c r="L45" s="436"/>
       <c r="M45" s="433"/>
       <c r="N45" s="434"/>
       <c r="Q45" s="3" t="s">
@@ -11273,19 +11129,19 @@
       <c r="A46" s="155" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="439" t="s">
+      <c r="B46" s="544" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="439"/>
-      <c r="D46" s="439"/>
-      <c r="E46" s="439"/>
-      <c r="F46" s="439"/>
-      <c r="G46" s="439"/>
-      <c r="H46" s="440"/>
-      <c r="I46" s="426"/>
-      <c r="J46" s="426"/>
-      <c r="K46" s="426"/>
-      <c r="L46" s="427"/>
+      <c r="C46" s="544"/>
+      <c r="D46" s="544"/>
+      <c r="E46" s="544"/>
+      <c r="F46" s="544"/>
+      <c r="G46" s="544"/>
+      <c r="H46" s="545"/>
+      <c r="I46" s="435"/>
+      <c r="J46" s="435"/>
+      <c r="K46" s="435"/>
+      <c r="L46" s="436"/>
       <c r="M46" s="433"/>
       <c r="N46" s="434"/>
       <c r="Q46" s="3" t="s">
@@ -11298,17 +11154,15 @@
         <v>10</v>
       </c>
       <c r="C47" s="163"/>
-      <c r="D47" s="613" t="s">
-        <v>404</v>
-      </c>
-      <c r="E47" s="614"/>
-      <c r="F47" s="614"/>
-      <c r="G47" s="614"/>
-      <c r="H47" s="615"/>
-      <c r="I47" s="426"/>
-      <c r="J47" s="426"/>
-      <c r="K47" s="426"/>
-      <c r="L47" s="427"/>
+      <c r="D47" s="450"/>
+      <c r="E47" s="451"/>
+      <c r="F47" s="451"/>
+      <c r="G47" s="451"/>
+      <c r="H47" s="452"/>
+      <c r="I47" s="435"/>
+      <c r="J47" s="435"/>
+      <c r="K47" s="435"/>
+      <c r="L47" s="436"/>
       <c r="M47" s="433"/>
       <c r="N47" s="434"/>
       <c r="Q47" s="3" t="s">
@@ -11321,17 +11175,15 @@
         <v>13</v>
       </c>
       <c r="C48" s="163"/>
-      <c r="D48" s="613" t="s">
-        <v>416</v>
-      </c>
-      <c r="E48" s="614"/>
-      <c r="F48" s="614"/>
-      <c r="G48" s="614"/>
-      <c r="H48" s="615"/>
-      <c r="I48" s="426"/>
-      <c r="J48" s="426"/>
-      <c r="K48" s="426"/>
-      <c r="L48" s="427"/>
+      <c r="D48" s="450"/>
+      <c r="E48" s="451"/>
+      <c r="F48" s="451"/>
+      <c r="G48" s="451"/>
+      <c r="H48" s="452"/>
+      <c r="I48" s="435"/>
+      <c r="J48" s="435"/>
+      <c r="K48" s="435"/>
+      <c r="L48" s="436"/>
       <c r="M48" s="433"/>
       <c r="N48" s="434"/>
       <c r="Q48" s="3" t="s">
@@ -11344,21 +11196,19 @@
         <v>17</v>
       </c>
       <c r="C49" s="221"/>
-      <c r="D49" s="430" t="s">
-        <v>415</v>
-      </c>
-      <c r="E49" s="431"/>
-      <c r="F49" s="431"/>
-      <c r="G49" s="431"/>
-      <c r="H49" s="432"/>
-      <c r="I49" s="428" t="s">
+      <c r="D49" s="612"/>
+      <c r="E49" s="613"/>
+      <c r="F49" s="613"/>
+      <c r="G49" s="613"/>
+      <c r="H49" s="614"/>
+      <c r="I49" s="610" t="s">
         <v>114</v>
       </c>
-      <c r="J49" s="428"/>
-      <c r="K49" s="428"/>
-      <c r="L49" s="428"/>
-      <c r="M49" s="428"/>
-      <c r="N49" s="429"/>
+      <c r="J49" s="610"/>
+      <c r="K49" s="610"/>
+      <c r="L49" s="610"/>
+      <c r="M49" s="610"/>
+      <c r="N49" s="611"/>
       <c r="Q49" s="3" t="s">
         <v>115</v>
       </c>
@@ -11374,47 +11224,47 @@
       <c r="F50" s="102"/>
       <c r="G50" s="102"/>
       <c r="H50" s="102"/>
-      <c r="I50" s="543" t="s">
+      <c r="I50" s="522" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="543"/>
-      <c r="K50" s="543"/>
-      <c r="L50" s="543"/>
-      <c r="M50" s="543"/>
-      <c r="N50" s="544"/>
+      <c r="J50" s="522"/>
+      <c r="K50" s="522"/>
+      <c r="L50" s="522"/>
+      <c r="M50" s="522"/>
+      <c r="N50" s="523"/>
       <c r="Q50" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="535" t="s">
+      <c r="A51" s="514" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="563" t="s">
+      <c r="B51" s="469" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="563"/>
-      <c r="D51" s="566" t="s">
+      <c r="C51" s="469"/>
+      <c r="D51" s="454" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="567"/>
-      <c r="F51" s="568"/>
-      <c r="G51" s="566" t="s">
+      <c r="E51" s="455"/>
+      <c r="F51" s="472"/>
+      <c r="G51" s="454" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="567"/>
-      <c r="I51" s="616"/>
-      <c r="J51" s="435" t="s">
+      <c r="H51" s="455"/>
+      <c r="I51" s="456"/>
+      <c r="J51" s="615" t="s">
         <v>123</v>
       </c>
-      <c r="K51" s="436"/>
-      <c r="L51" s="608" t="s">
+      <c r="K51" s="616"/>
+      <c r="L51" s="445" t="s">
         <v>124</v>
       </c>
-      <c r="M51" s="537" t="s">
+      <c r="M51" s="516" t="s">
         <v>125</v>
       </c>
-      <c r="N51" s="533" t="s">
+      <c r="N51" s="512" t="s">
         <v>126</v>
       </c>
       <c r="Q51" s="3" t="s">
@@ -11422,43 +11272,43 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="536"/>
-      <c r="B52" s="564"/>
-      <c r="C52" s="564"/>
-      <c r="D52" s="569"/>
-      <c r="E52" s="570"/>
-      <c r="F52" s="571"/>
-      <c r="G52" s="569"/>
-      <c r="H52" s="570"/>
-      <c r="I52" s="617"/>
-      <c r="J52" s="437"/>
-      <c r="K52" s="438"/>
-      <c r="L52" s="608"/>
-      <c r="M52" s="537"/>
-      <c r="N52" s="533"/>
+      <c r="A52" s="515"/>
+      <c r="B52" s="470"/>
+      <c r="C52" s="470"/>
+      <c r="D52" s="457"/>
+      <c r="E52" s="458"/>
+      <c r="F52" s="473"/>
+      <c r="G52" s="457"/>
+      <c r="H52" s="458"/>
+      <c r="I52" s="459"/>
+      <c r="J52" s="617"/>
+      <c r="K52" s="618"/>
+      <c r="L52" s="445"/>
+      <c r="M52" s="516"/>
+      <c r="N52" s="512"/>
       <c r="Q52" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="234"/>
-      <c r="B53" s="565"/>
-      <c r="C53" s="565"/>
-      <c r="D53" s="572"/>
-      <c r="E53" s="573"/>
-      <c r="F53" s="553"/>
-      <c r="G53" s="572"/>
-      <c r="H53" s="573"/>
-      <c r="I53" s="618"/>
+      <c r="B53" s="471"/>
+      <c r="C53" s="471"/>
+      <c r="D53" s="460"/>
+      <c r="E53" s="461"/>
+      <c r="F53" s="474"/>
+      <c r="G53" s="460"/>
+      <c r="H53" s="461"/>
+      <c r="I53" s="462"/>
       <c r="J53" s="107" t="s">
         <v>129</v>
       </c>
       <c r="K53" s="108" t="s">
         <v>130</v>
       </c>
-      <c r="L53" s="609"/>
-      <c r="M53" s="538"/>
-      <c r="N53" s="534"/>
+      <c r="L53" s="446"/>
+      <c r="M53" s="517"/>
+      <c r="N53" s="513"/>
       <c r="O53" s="109"/>
       <c r="P53" s="109"/>
       <c r="Q53" s="3" t="s">
@@ -11471,20 +11321,14 @@
         <v>132</v>
       </c>
       <c r="C54" s="240"/>
-      <c r="D54" s="574" t="s">
-        <v>417</v>
-      </c>
-      <c r="E54" s="575"/>
-      <c r="F54" s="576"/>
-      <c r="G54" s="610"/>
-      <c r="H54" s="611"/>
-      <c r="I54" s="612"/>
-      <c r="J54" s="23">
-        <v>38145</v>
-      </c>
-      <c r="K54" s="233">
-        <v>40238</v>
-      </c>
+      <c r="D54" s="475"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="477"/>
+      <c r="G54" s="447"/>
+      <c r="H54" s="448"/>
+      <c r="I54" s="449"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="233"/>
       <c r="L54" s="168"/>
       <c r="M54" s="15"/>
       <c r="N54" s="162"/>
@@ -11498,20 +11342,14 @@
         <v>134</v>
       </c>
       <c r="C55" s="240"/>
-      <c r="D55" s="574" t="s">
-        <v>418</v>
-      </c>
-      <c r="E55" s="575"/>
-      <c r="F55" s="576"/>
-      <c r="G55" s="610"/>
-      <c r="H55" s="611"/>
-      <c r="I55" s="612"/>
-      <c r="J55" s="233">
-        <v>40336</v>
-      </c>
-      <c r="K55" s="233">
-        <v>41699</v>
-      </c>
+      <c r="D55" s="475"/>
+      <c r="E55" s="476"/>
+      <c r="F55" s="477"/>
+      <c r="G55" s="447"/>
+      <c r="H55" s="448"/>
+      <c r="I55" s="449"/>
+      <c r="J55" s="233"/>
+      <c r="K55" s="233"/>
       <c r="L55" s="243"/>
       <c r="M55" s="16"/>
       <c r="N55" s="162"/>
@@ -11525,12 +11363,12 @@
         <v>136</v>
       </c>
       <c r="C56" s="240"/>
-      <c r="D56" s="574"/>
-      <c r="E56" s="575"/>
-      <c r="F56" s="576"/>
-      <c r="G56" s="423"/>
-      <c r="H56" s="424"/>
-      <c r="I56" s="425"/>
+      <c r="D56" s="475"/>
+      <c r="E56" s="476"/>
+      <c r="F56" s="477"/>
+      <c r="G56" s="463"/>
+      <c r="H56" s="464"/>
+      <c r="I56" s="465"/>
       <c r="J56" s="23"/>
       <c r="K56" s="24"/>
       <c r="L56" s="168"/>
@@ -11546,26 +11384,16 @@
         <v>138</v>
       </c>
       <c r="C57" s="240"/>
-      <c r="D57" s="574" t="s">
-        <v>419</v>
-      </c>
-      <c r="E57" s="575"/>
-      <c r="F57" s="576"/>
-      <c r="G57" s="423"/>
-      <c r="H57" s="424"/>
-      <c r="I57" s="425"/>
-      <c r="J57" s="233">
-        <v>41797</v>
-      </c>
-      <c r="K57" s="233">
-        <v>43290</v>
-      </c>
-      <c r="L57" s="168" t="s">
-        <v>420</v>
-      </c>
-      <c r="M57" s="16">
-        <v>2018</v>
-      </c>
+      <c r="D57" s="475"/>
+      <c r="E57" s="476"/>
+      <c r="F57" s="477"/>
+      <c r="G57" s="463"/>
+      <c r="H57" s="464"/>
+      <c r="I57" s="465"/>
+      <c r="J57" s="233"/>
+      <c r="K57" s="233"/>
+      <c r="L57" s="168"/>
+      <c r="M57" s="16"/>
       <c r="N57" s="162"/>
       <c r="Q57" s="3" t="s">
         <v>139</v>
@@ -11577,12 +11405,12 @@
         <v>140</v>
       </c>
       <c r="C58" s="242"/>
-      <c r="D58" s="577"/>
-      <c r="E58" s="578"/>
-      <c r="F58" s="579"/>
-      <c r="G58" s="560"/>
-      <c r="H58" s="561"/>
-      <c r="I58" s="562"/>
+      <c r="D58" s="478"/>
+      <c r="E58" s="479"/>
+      <c r="F58" s="480"/>
+      <c r="G58" s="466"/>
+      <c r="H58" s="467"/>
+      <c r="I58" s="468"/>
       <c r="J58" s="237"/>
       <c r="K58" s="238"/>
       <c r="L58" s="17"/>
@@ -11593,70 +11421,66 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="597" t="s">
+      <c r="A59" s="427" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="598"/>
-      <c r="C59" s="598"/>
-      <c r="D59" s="598"/>
-      <c r="E59" s="598"/>
-      <c r="F59" s="598"/>
-      <c r="G59" s="598"/>
-      <c r="H59" s="598"/>
-      <c r="I59" s="598"/>
-      <c r="J59" s="598"/>
-      <c r="K59" s="598"/>
-      <c r="L59" s="598"/>
-      <c r="M59" s="598"/>
-      <c r="N59" s="599"/>
+      <c r="B59" s="428"/>
+      <c r="C59" s="428"/>
+      <c r="D59" s="428"/>
+      <c r="E59" s="428"/>
+      <c r="F59" s="428"/>
+      <c r="G59" s="428"/>
+      <c r="H59" s="428"/>
+      <c r="I59" s="428"/>
+      <c r="J59" s="428"/>
+      <c r="K59" s="428"/>
+      <c r="L59" s="428"/>
+      <c r="M59" s="428"/>
+      <c r="N59" s="429"/>
       <c r="Q59" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="594" t="s">
+      <c r="A60" s="424" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="595"/>
-      <c r="C60" s="596"/>
-      <c r="D60" s="603" t="s">
-        <v>443</v>
-      </c>
-      <c r="E60" s="604"/>
-      <c r="F60" s="604"/>
-      <c r="G60" s="604"/>
-      <c r="H60" s="604"/>
-      <c r="I60" s="605"/>
-      <c r="J60" s="606" t="s">
+      <c r="B60" s="425"/>
+      <c r="C60" s="426"/>
+      <c r="D60" s="440"/>
+      <c r="E60" s="441"/>
+      <c r="F60" s="441"/>
+      <c r="G60" s="441"/>
+      <c r="H60" s="441"/>
+      <c r="I60" s="442"/>
+      <c r="J60" s="443" t="s">
         <v>144</v>
       </c>
-      <c r="K60" s="607"/>
-      <c r="L60" s="600" t="s">
-        <v>442</v>
-      </c>
-      <c r="M60" s="601"/>
-      <c r="N60" s="602"/>
+      <c r="K60" s="444"/>
+      <c r="L60" s="430"/>
+      <c r="M60" s="431"/>
+      <c r="N60" s="432"/>
       <c r="Q60" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="146" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="593" t="s">
+      <c r="A61" s="423" t="s">
         <v>402</v>
       </c>
-      <c r="B61" s="593"/>
-      <c r="C61" s="593"/>
-      <c r="D61" s="593"/>
-      <c r="E61" s="593"/>
-      <c r="F61" s="593"/>
-      <c r="G61" s="593"/>
-      <c r="H61" s="593"/>
-      <c r="I61" s="593"/>
-      <c r="J61" s="593"/>
-      <c r="K61" s="593"/>
-      <c r="L61" s="593"/>
-      <c r="M61" s="593"/>
-      <c r="N61" s="593"/>
+      <c r="B61" s="423"/>
+      <c r="C61" s="423"/>
+      <c r="D61" s="423"/>
+      <c r="E61" s="423"/>
+      <c r="F61" s="423"/>
+      <c r="G61" s="423"/>
+      <c r="H61" s="423"/>
+      <c r="I61" s="423"/>
+      <c r="J61" s="423"/>
+      <c r="K61" s="423"/>
+      <c r="L61" s="423"/>
+      <c r="M61" s="423"/>
+      <c r="N61" s="423"/>
       <c r="Q61" s="256" t="s">
         <v>146</v>
       </c>
@@ -15385,6 +15209,122 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="140">
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:N49"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="J51:K52"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="I19:K20"/>
+    <mergeCell ref="L19:N20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D25:F26"/>
+    <mergeCell ref="D27:F28"/>
+    <mergeCell ref="D29:F30"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D17:F18"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="I50:N50"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="B51:C53"/>
+    <mergeCell ref="D51:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I36:L36"/>
     <mergeCell ref="A61:N61"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A59:N59"/>
@@ -15409,122 +15349,6 @@
     <mergeCell ref="G51:I53"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="G56:I56"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="B51:C53"/>
-    <mergeCell ref="D51:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="I50:N50"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="I19:K20"/>
-    <mergeCell ref="L19:N20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D25:F26"/>
-    <mergeCell ref="D27:F28"/>
-    <mergeCell ref="D29:F30"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="D17:F18"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:N49"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -15732,20 +15556,19 @@
     <hyperlink ref="Q216" r:id="rId203" display="http://www.state.gov/p/af/ci/zi/" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
     <hyperlink ref="Q60" r:id="rId204" display="http://www.state.gov/p/eur/ci/cy/" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
     <hyperlink ref="Q61" r:id="rId205" display="http://www.state.gov/p/eur/ci/ez/" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="I34" r:id="rId206" xr:uid="{0FAACD08-FE0E-44A1-9762-E74D7EFAA138}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15" right="0.12" top="0.36" bottom="0.12" header="0.24" footer="0.12"/>
-  <pageSetup paperSize="269" scale="73" orientation="portrait" r:id="rId207"/>
+  <pageSetup paperSize="269" scale="73" orientation="portrait" r:id="rId206"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId208"/>
-  <legacyDrawing r:id="rId209"/>
+  <drawing r:id="rId207"/>
+  <legacyDrawing r:id="rId208"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId210" name="Drop Down 31">
+            <control shapeId="1055" r:id="rId209" name="Drop Down 31">
               <controlPr locked="0" defaultSize="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15767,7 +15590,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId211" name="Check Box 21">
+            <control shapeId="1045" r:id="rId210" name="Check Box 21">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15789,7 +15612,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId212" name="Check Box 22">
+            <control shapeId="1046" r:id="rId211" name="Check Box 22">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15811,7 +15634,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId213" name="Check Box 25">
+            <control shapeId="1049" r:id="rId212" name="Check Box 25">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15833,7 +15656,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId214" name="Check Box 26">
+            <control shapeId="1050" r:id="rId213" name="Check Box 26">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15855,7 +15678,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId215" name="Check Box 34">
+            <control shapeId="1058" r:id="rId214" name="Check Box 34">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15877,7 +15700,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId216" name="Check Box 35">
+            <control shapeId="1059" r:id="rId215" name="Check Box 35">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15899,7 +15722,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId217" name="Check Box 36">
+            <control shapeId="1060" r:id="rId216" name="Check Box 36">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15921,7 +15744,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId218" name="Check Box 37">
+            <control shapeId="1061" r:id="rId217" name="Check Box 37">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15943,7 +15766,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId219" name="Check Box 38">
+            <control shapeId="1062" r:id="rId218" name="Check Box 38">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15965,7 +15788,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId220" name="Check Box 39">
+            <control shapeId="1063" r:id="rId219" name="Check Box 39">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15987,7 +15810,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId221" name="Check Box 40">
+            <control shapeId="1064" r:id="rId220" name="Check Box 40">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16034,68 +15857,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="649"/>
-      <c r="B1" s="650"/>
-      <c r="C1" s="650"/>
-      <c r="D1" s="650"/>
-      <c r="E1" s="650"/>
-      <c r="F1" s="650"/>
-      <c r="G1" s="650"/>
-      <c r="H1" s="650"/>
-      <c r="I1" s="650"/>
-      <c r="J1" s="650"/>
-      <c r="K1" s="651"/>
+      <c r="A1" s="619"/>
+      <c r="B1" s="620"/>
+      <c r="C1" s="620"/>
+      <c r="D1" s="620"/>
+      <c r="E1" s="620"/>
+      <c r="F1" s="620"/>
+      <c r="G1" s="620"/>
+      <c r="H1" s="620"/>
+      <c r="I1" s="620"/>
+      <c r="J1" s="620"/>
+      <c r="K1" s="621"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="660" t="s">
+      <c r="A2" s="632" t="s">
         <v>303</v>
       </c>
-      <c r="B2" s="661"/>
-      <c r="C2" s="661"/>
-      <c r="D2" s="661"/>
-      <c r="E2" s="661"/>
-      <c r="F2" s="661"/>
-      <c r="G2" s="661"/>
-      <c r="H2" s="661"/>
-      <c r="I2" s="661"/>
-      <c r="J2" s="661"/>
-      <c r="K2" s="662"/>
+      <c r="B2" s="633"/>
+      <c r="C2" s="633"/>
+      <c r="D2" s="633"/>
+      <c r="E2" s="633"/>
+      <c r="F2" s="633"/>
+      <c r="G2" s="633"/>
+      <c r="H2" s="633"/>
+      <c r="I2" s="633"/>
+      <c r="J2" s="633"/>
+      <c r="K2" s="634"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="143" t="s">
         <v>304</v>
       </c>
-      <c r="B3" s="652" t="s">
+      <c r="B3" s="622" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="652"/>
-      <c r="D3" s="652"/>
-      <c r="E3" s="653"/>
-      <c r="F3" s="658" t="s">
+      <c r="C3" s="622"/>
+      <c r="D3" s="622"/>
+      <c r="E3" s="623"/>
+      <c r="F3" s="630" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="654" t="s">
+      <c r="G3" s="626" t="s">
         <v>307</v>
       </c>
-      <c r="H3" s="653"/>
-      <c r="I3" s="654" t="s">
+      <c r="H3" s="623"/>
+      <c r="I3" s="626" t="s">
         <v>308</v>
       </c>
-      <c r="J3" s="656" t="s">
+      <c r="J3" s="628" t="s">
         <v>309</v>
       </c>
-      <c r="K3" s="657"/>
+      <c r="K3" s="629"/>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="641"/>
-      <c r="C4" s="641"/>
-      <c r="D4" s="641"/>
-      <c r="E4" s="642"/>
-      <c r="F4" s="659"/>
-      <c r="G4" s="655"/>
-      <c r="H4" s="642"/>
-      <c r="I4" s="655"/>
+      <c r="B4" s="624"/>
+      <c r="C4" s="624"/>
+      <c r="D4" s="624"/>
+      <c r="E4" s="625"/>
+      <c r="F4" s="631"/>
+      <c r="G4" s="627"/>
+      <c r="H4" s="625"/>
+      <c r="I4" s="627"/>
       <c r="J4" s="5" t="s">
         <v>310</v>
       </c>
@@ -16104,125 +15927,125 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="666"/>
-      <c r="B5" s="619"/>
-      <c r="C5" s="619"/>
-      <c r="D5" s="619"/>
-      <c r="E5" s="619"/>
+      <c r="A5" s="638"/>
+      <c r="B5" s="639"/>
+      <c r="C5" s="639"/>
+      <c r="D5" s="639"/>
+      <c r="E5" s="639"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="665"/>
-      <c r="H5" s="665"/>
+      <c r="G5" s="637"/>
+      <c r="H5" s="637"/>
       <c r="I5" s="274"/>
       <c r="J5" s="8"/>
       <c r="K5" s="19"/>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="666"/>
-      <c r="B6" s="619"/>
-      <c r="C6" s="619"/>
-      <c r="D6" s="619"/>
-      <c r="E6" s="619"/>
+      <c r="A6" s="638"/>
+      <c r="B6" s="639"/>
+      <c r="C6" s="639"/>
+      <c r="D6" s="639"/>
+      <c r="E6" s="639"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="670"/>
-      <c r="H6" s="671"/>
+      <c r="G6" s="645"/>
+      <c r="H6" s="646"/>
       <c r="I6" s="274"/>
       <c r="J6" s="8"/>
       <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="666"/>
-      <c r="B7" s="619"/>
-      <c r="C7" s="619"/>
-      <c r="D7" s="619"/>
-      <c r="E7" s="619"/>
+      <c r="A7" s="638"/>
+      <c r="B7" s="639"/>
+      <c r="C7" s="639"/>
+      <c r="D7" s="639"/>
+      <c r="E7" s="639"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="665"/>
-      <c r="H7" s="665"/>
+      <c r="G7" s="637"/>
+      <c r="H7" s="637"/>
       <c r="I7" s="274"/>
       <c r="J7" s="8"/>
       <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="666"/>
-      <c r="B8" s="619"/>
-      <c r="C8" s="619"/>
-      <c r="D8" s="619"/>
-      <c r="E8" s="619"/>
+      <c r="A8" s="638"/>
+      <c r="B8" s="639"/>
+      <c r="C8" s="639"/>
+      <c r="D8" s="639"/>
+      <c r="E8" s="639"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="665"/>
-      <c r="H8" s="665"/>
+      <c r="G8" s="637"/>
+      <c r="H8" s="637"/>
       <c r="I8" s="274"/>
       <c r="J8" s="8"/>
       <c r="K8" s="19"/>
     </row>
     <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="666"/>
-      <c r="B9" s="619"/>
-      <c r="C9" s="619"/>
-      <c r="D9" s="619"/>
-      <c r="E9" s="619"/>
+      <c r="A9" s="638"/>
+      <c r="B9" s="639"/>
+      <c r="C9" s="639"/>
+      <c r="D9" s="639"/>
+      <c r="E9" s="639"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="665"/>
-      <c r="H9" s="665"/>
+      <c r="G9" s="637"/>
+      <c r="H9" s="637"/>
       <c r="I9" s="274"/>
       <c r="J9" s="8"/>
       <c r="K9" s="19"/>
     </row>
     <row r="10" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="666"/>
-      <c r="B10" s="619"/>
-      <c r="C10" s="619"/>
-      <c r="D10" s="619"/>
-      <c r="E10" s="619"/>
+      <c r="A10" s="638"/>
+      <c r="B10" s="639"/>
+      <c r="C10" s="639"/>
+      <c r="D10" s="639"/>
+      <c r="E10" s="639"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="665"/>
-      <c r="H10" s="665"/>
+      <c r="G10" s="637"/>
+      <c r="H10" s="637"/>
       <c r="I10" s="274"/>
       <c r="J10" s="8"/>
       <c r="K10" s="19"/>
     </row>
     <row r="11" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="638"/>
-      <c r="B11" s="629"/>
-      <c r="C11" s="629"/>
-      <c r="D11" s="629"/>
-      <c r="E11" s="629"/>
+      <c r="A11" s="652"/>
+      <c r="B11" s="653"/>
+      <c r="C11" s="653"/>
+      <c r="D11" s="653"/>
+      <c r="E11" s="653"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="634"/>
-      <c r="H11" s="634"/>
+      <c r="G11" s="660"/>
+      <c r="H11" s="660"/>
       <c r="I11" s="275"/>
       <c r="J11" s="10"/>
       <c r="K11" s="20"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="643" t="s">
+      <c r="A12" s="654" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="644"/>
-      <c r="C12" s="644"/>
-      <c r="D12" s="644"/>
-      <c r="E12" s="644"/>
-      <c r="F12" s="644"/>
-      <c r="G12" s="644"/>
-      <c r="H12" s="644"/>
-      <c r="I12" s="644"/>
-      <c r="J12" s="644"/>
-      <c r="K12" s="645"/>
+      <c r="B12" s="655"/>
+      <c r="C12" s="655"/>
+      <c r="D12" s="655"/>
+      <c r="E12" s="655"/>
+      <c r="F12" s="655"/>
+      <c r="G12" s="655"/>
+      <c r="H12" s="655"/>
+      <c r="I12" s="655"/>
+      <c r="J12" s="655"/>
+      <c r="K12" s="656"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="646" t="s">
+      <c r="A13" s="657" t="s">
         <v>312</v>
       </c>
-      <c r="B13" s="647"/>
-      <c r="C13" s="647"/>
-      <c r="D13" s="647"/>
-      <c r="E13" s="647"/>
-      <c r="F13" s="647"/>
-      <c r="G13" s="647"/>
-      <c r="H13" s="647"/>
-      <c r="I13" s="647"/>
-      <c r="J13" s="647"/>
-      <c r="K13" s="648"/>
+      <c r="B13" s="658"/>
+      <c r="C13" s="658"/>
+      <c r="D13" s="658"/>
+      <c r="E13" s="658"/>
+      <c r="F13" s="658"/>
+      <c r="G13" s="658"/>
+      <c r="H13" s="658"/>
+      <c r="I13" s="658"/>
+      <c r="J13" s="658"/>
+      <c r="K13" s="659"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="218" t="s">
@@ -16243,504 +16066,468 @@
       <c r="A15" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B15" s="639" t="s">
+      <c r="B15" s="643" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="640"/>
-      <c r="D15" s="669" t="s">
+      <c r="C15" s="644"/>
+      <c r="D15" s="642" t="s">
         <v>315</v>
       </c>
-      <c r="E15" s="639"/>
-      <c r="F15" s="640"/>
-      <c r="G15" s="669" t="s">
+      <c r="E15" s="643"/>
+      <c r="F15" s="644"/>
+      <c r="G15" s="642" t="s">
         <v>316</v>
       </c>
-      <c r="H15" s="639"/>
-      <c r="I15" s="640"/>
-      <c r="J15" s="624" t="s">
+      <c r="H15" s="643"/>
+      <c r="I15" s="644"/>
+      <c r="J15" s="663" t="s">
         <v>317</v>
       </c>
-      <c r="K15" s="663" t="s">
+      <c r="K15" s="635" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="641"/>
-      <c r="C16" s="642"/>
-      <c r="D16" s="669"/>
-      <c r="E16" s="639"/>
-      <c r="F16" s="640"/>
-      <c r="G16" s="669"/>
-      <c r="H16" s="639"/>
-      <c r="I16" s="640"/>
-      <c r="J16" s="624"/>
-      <c r="K16" s="663"/>
+      <c r="B16" s="624"/>
+      <c r="C16" s="625"/>
+      <c r="D16" s="642"/>
+      <c r="E16" s="643"/>
+      <c r="F16" s="644"/>
+      <c r="G16" s="642"/>
+      <c r="H16" s="643"/>
+      <c r="I16" s="644"/>
+      <c r="J16" s="663"/>
+      <c r="K16" s="635"/>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="667" t="s">
+      <c r="A17" s="640" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="668"/>
+      <c r="B17" s="641"/>
       <c r="C17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="655"/>
-      <c r="E17" s="641"/>
-      <c r="F17" s="642"/>
-      <c r="G17" s="655"/>
-      <c r="H17" s="641"/>
-      <c r="I17" s="642"/>
-      <c r="J17" s="625"/>
-      <c r="K17" s="664"/>
+      <c r="D17" s="627"/>
+      <c r="E17" s="624"/>
+      <c r="F17" s="625"/>
+      <c r="G17" s="627"/>
+      <c r="H17" s="624"/>
+      <c r="I17" s="625"/>
+      <c r="J17" s="664"/>
+      <c r="K17" s="636"/>
     </row>
     <row r="18" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="620">
-        <v>43952</v>
-      </c>
-      <c r="B18" s="621"/>
-      <c r="C18" s="21">
-        <v>44593</v>
-      </c>
-      <c r="D18" s="619" t="s">
-        <v>427</v>
-      </c>
-      <c r="E18" s="619"/>
-      <c r="F18" s="619"/>
-      <c r="G18" s="619" t="s">
-        <v>426</v>
-      </c>
-      <c r="H18" s="619"/>
-      <c r="I18" s="619"/>
+      <c r="A18" s="650"/>
+      <c r="B18" s="651"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="639"/>
+      <c r="E18" s="639"/>
+      <c r="F18" s="639"/>
+      <c r="G18" s="639"/>
+      <c r="H18" s="639"/>
+      <c r="I18" s="639"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="620">
-        <v>44868</v>
-      </c>
-      <c r="B19" s="621"/>
-      <c r="C19" s="21">
-        <v>45202</v>
-      </c>
-      <c r="D19" s="619" t="s">
-        <v>429</v>
-      </c>
-      <c r="E19" s="619"/>
-      <c r="F19" s="619"/>
-      <c r="G19" s="619" t="s">
-        <v>428</v>
-      </c>
-      <c r="H19" s="619"/>
-      <c r="I19" s="619"/>
+      <c r="A19" s="650"/>
+      <c r="B19" s="651"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="639"/>
+      <c r="E19" s="639"/>
+      <c r="F19" s="639"/>
+      <c r="G19" s="639"/>
+      <c r="H19" s="639"/>
+      <c r="I19" s="639"/>
       <c r="J19" s="8"/>
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="620" t="s">
-        <v>432</v>
-      </c>
-      <c r="B20" s="621"/>
-      <c r="C20" s="21" t="s">
-        <v>433</v>
-      </c>
-      <c r="D20" s="619" t="s">
-        <v>430</v>
-      </c>
-      <c r="E20" s="619"/>
-      <c r="F20" s="619"/>
-      <c r="G20" s="619" t="s">
-        <v>431</v>
-      </c>
-      <c r="H20" s="619"/>
-      <c r="I20" s="619"/>
+      <c r="A20" s="650"/>
+      <c r="B20" s="651"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="639"/>
+      <c r="E20" s="639"/>
+      <c r="F20" s="639"/>
+      <c r="G20" s="639"/>
+      <c r="H20" s="639"/>
+      <c r="I20" s="639"/>
       <c r="J20" s="8"/>
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="620" t="s">
-        <v>436</v>
-      </c>
-      <c r="B21" s="621"/>
-      <c r="C21" s="21" t="s">
-        <v>437</v>
-      </c>
-      <c r="D21" s="619" t="s">
-        <v>434</v>
-      </c>
-      <c r="E21" s="619"/>
-      <c r="F21" s="619"/>
-      <c r="G21" s="619" t="s">
-        <v>435</v>
-      </c>
-      <c r="H21" s="619"/>
-      <c r="I21" s="619"/>
+      <c r="A21" s="650"/>
+      <c r="B21" s="651"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="639"/>
+      <c r="E21" s="639"/>
+      <c r="F21" s="639"/>
+      <c r="G21" s="639"/>
+      <c r="H21" s="639"/>
+      <c r="I21" s="639"/>
       <c r="J21" s="8"/>
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="620"/>
-      <c r="B22" s="621"/>
+      <c r="A22" s="650"/>
+      <c r="B22" s="651"/>
       <c r="C22" s="21"/>
-      <c r="D22" s="619"/>
-      <c r="E22" s="619"/>
-      <c r="F22" s="619"/>
-      <c r="G22" s="619"/>
-      <c r="H22" s="619"/>
-      <c r="I22" s="619"/>
+      <c r="D22" s="639"/>
+      <c r="E22" s="639"/>
+      <c r="F22" s="639"/>
+      <c r="G22" s="639"/>
+      <c r="H22" s="639"/>
+      <c r="I22" s="639"/>
       <c r="J22" s="8"/>
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="620"/>
-      <c r="B23" s="621"/>
+      <c r="A23" s="650"/>
+      <c r="B23" s="651"/>
       <c r="C23" s="21"/>
-      <c r="D23" s="619"/>
-      <c r="E23" s="619"/>
-      <c r="F23" s="619"/>
-      <c r="G23" s="619"/>
-      <c r="H23" s="619"/>
-      <c r="I23" s="619"/>
+      <c r="D23" s="639"/>
+      <c r="E23" s="639"/>
+      <c r="F23" s="639"/>
+      <c r="G23" s="639"/>
+      <c r="H23" s="639"/>
+      <c r="I23" s="639"/>
       <c r="J23" s="8"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="620"/>
-      <c r="B24" s="621"/>
+      <c r="A24" s="650"/>
+      <c r="B24" s="651"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="619"/>
-      <c r="E24" s="619"/>
-      <c r="F24" s="619"/>
-      <c r="G24" s="619"/>
-      <c r="H24" s="619"/>
-      <c r="I24" s="619"/>
+      <c r="D24" s="639"/>
+      <c r="E24" s="639"/>
+      <c r="F24" s="639"/>
+      <c r="G24" s="639"/>
+      <c r="H24" s="639"/>
+      <c r="I24" s="639"/>
       <c r="J24" s="8"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="620"/>
-      <c r="B25" s="621"/>
+      <c r="A25" s="650"/>
+      <c r="B25" s="651"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="619"/>
-      <c r="E25" s="619"/>
-      <c r="F25" s="619"/>
-      <c r="G25" s="619"/>
-      <c r="H25" s="619"/>
-      <c r="I25" s="619"/>
+      <c r="D25" s="639"/>
+      <c r="E25" s="639"/>
+      <c r="F25" s="639"/>
+      <c r="G25" s="639"/>
+      <c r="H25" s="639"/>
+      <c r="I25" s="639"/>
       <c r="J25" s="8"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="620"/>
-      <c r="B26" s="621"/>
+      <c r="A26" s="650"/>
+      <c r="B26" s="651"/>
       <c r="C26" s="21"/>
-      <c r="D26" s="619"/>
-      <c r="E26" s="619"/>
-      <c r="F26" s="619"/>
-      <c r="G26" s="619"/>
-      <c r="H26" s="619"/>
-      <c r="I26" s="619"/>
+      <c r="D26" s="639"/>
+      <c r="E26" s="639"/>
+      <c r="F26" s="639"/>
+      <c r="G26" s="639"/>
+      <c r="H26" s="639"/>
+      <c r="I26" s="639"/>
       <c r="J26" s="8"/>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="620"/>
-      <c r="B27" s="621"/>
+      <c r="A27" s="650"/>
+      <c r="B27" s="651"/>
       <c r="C27" s="21"/>
-      <c r="D27" s="619"/>
-      <c r="E27" s="619"/>
-      <c r="F27" s="619"/>
-      <c r="G27" s="619"/>
-      <c r="H27" s="619"/>
-      <c r="I27" s="619"/>
+      <c r="D27" s="639"/>
+      <c r="E27" s="639"/>
+      <c r="F27" s="639"/>
+      <c r="G27" s="639"/>
+      <c r="H27" s="639"/>
+      <c r="I27" s="639"/>
       <c r="J27" s="8"/>
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="620"/>
-      <c r="B28" s="621"/>
+      <c r="A28" s="650"/>
+      <c r="B28" s="651"/>
       <c r="C28" s="21"/>
-      <c r="D28" s="619"/>
-      <c r="E28" s="619"/>
-      <c r="F28" s="619"/>
-      <c r="G28" s="619"/>
-      <c r="H28" s="619"/>
-      <c r="I28" s="619"/>
+      <c r="D28" s="639"/>
+      <c r="E28" s="639"/>
+      <c r="F28" s="639"/>
+      <c r="G28" s="639"/>
+      <c r="H28" s="639"/>
+      <c r="I28" s="639"/>
       <c r="J28" s="8"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="620"/>
-      <c r="B29" s="621"/>
+      <c r="A29" s="650"/>
+      <c r="B29" s="651"/>
       <c r="C29" s="21"/>
-      <c r="D29" s="619"/>
-      <c r="E29" s="619"/>
-      <c r="F29" s="619"/>
-      <c r="G29" s="619"/>
-      <c r="H29" s="619"/>
-      <c r="I29" s="619"/>
+      <c r="D29" s="639"/>
+      <c r="E29" s="639"/>
+      <c r="F29" s="639"/>
+      <c r="G29" s="639"/>
+      <c r="H29" s="639"/>
+      <c r="I29" s="639"/>
       <c r="J29" s="8"/>
       <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="620"/>
-      <c r="B30" s="621"/>
+      <c r="A30" s="650"/>
+      <c r="B30" s="651"/>
       <c r="C30" s="21"/>
-      <c r="D30" s="619"/>
-      <c r="E30" s="619"/>
-      <c r="F30" s="619"/>
-      <c r="G30" s="619"/>
-      <c r="H30" s="619"/>
-      <c r="I30" s="619"/>
+      <c r="D30" s="639"/>
+      <c r="E30" s="639"/>
+      <c r="F30" s="639"/>
+      <c r="G30" s="639"/>
+      <c r="H30" s="639"/>
+      <c r="I30" s="639"/>
       <c r="J30" s="8"/>
       <c r="K30" s="9"/>
     </row>
     <row r="31" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="620"/>
-      <c r="B31" s="621"/>
+      <c r="A31" s="650"/>
+      <c r="B31" s="651"/>
       <c r="C31" s="21"/>
-      <c r="D31" s="619"/>
-      <c r="E31" s="619"/>
-      <c r="F31" s="619"/>
-      <c r="G31" s="619"/>
-      <c r="H31" s="619"/>
-      <c r="I31" s="619"/>
+      <c r="D31" s="639"/>
+      <c r="E31" s="639"/>
+      <c r="F31" s="639"/>
+      <c r="G31" s="639"/>
+      <c r="H31" s="639"/>
+      <c r="I31" s="639"/>
       <c r="J31" s="8"/>
       <c r="K31" s="9"/>
     </row>
     <row r="32" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="620"/>
-      <c r="B32" s="621"/>
+      <c r="A32" s="650"/>
+      <c r="B32" s="651"/>
       <c r="C32" s="21"/>
-      <c r="D32" s="619"/>
-      <c r="E32" s="619"/>
-      <c r="F32" s="619"/>
-      <c r="G32" s="619"/>
-      <c r="H32" s="619"/>
-      <c r="I32" s="619"/>
+      <c r="D32" s="639"/>
+      <c r="E32" s="639"/>
+      <c r="F32" s="639"/>
+      <c r="G32" s="639"/>
+      <c r="H32" s="639"/>
+      <c r="I32" s="639"/>
       <c r="J32" s="8"/>
       <c r="K32" s="9"/>
     </row>
     <row r="33" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="620"/>
-      <c r="B33" s="621"/>
+      <c r="A33" s="650"/>
+      <c r="B33" s="651"/>
       <c r="C33" s="21"/>
-      <c r="D33" s="619"/>
-      <c r="E33" s="619"/>
-      <c r="F33" s="619"/>
-      <c r="G33" s="619"/>
-      <c r="H33" s="619"/>
-      <c r="I33" s="619"/>
+      <c r="D33" s="639"/>
+      <c r="E33" s="639"/>
+      <c r="F33" s="639"/>
+      <c r="G33" s="639"/>
+      <c r="H33" s="639"/>
+      <c r="I33" s="639"/>
       <c r="J33" s="8"/>
       <c r="K33" s="9"/>
     </row>
     <row r="34" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="620"/>
-      <c r="B34" s="621"/>
+      <c r="A34" s="650"/>
+      <c r="B34" s="651"/>
       <c r="C34" s="21"/>
-      <c r="D34" s="619"/>
-      <c r="E34" s="619"/>
-      <c r="F34" s="619"/>
-      <c r="G34" s="619"/>
-      <c r="H34" s="619"/>
-      <c r="I34" s="619"/>
+      <c r="D34" s="639"/>
+      <c r="E34" s="639"/>
+      <c r="F34" s="639"/>
+      <c r="G34" s="639"/>
+      <c r="H34" s="639"/>
+      <c r="I34" s="639"/>
       <c r="J34" s="8"/>
       <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:12" s="12" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="620"/>
-      <c r="B35" s="621"/>
+      <c r="A35" s="650"/>
+      <c r="B35" s="651"/>
       <c r="C35" s="21"/>
-      <c r="D35" s="619"/>
-      <c r="E35" s="619"/>
-      <c r="F35" s="619"/>
-      <c r="G35" s="619"/>
-      <c r="H35" s="619"/>
-      <c r="I35" s="619"/>
+      <c r="D35" s="639"/>
+      <c r="E35" s="639"/>
+      <c r="F35" s="639"/>
+      <c r="G35" s="639"/>
+      <c r="H35" s="639"/>
+      <c r="I35" s="639"/>
       <c r="J35" s="8"/>
       <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="620"/>
-      <c r="B36" s="621"/>
+      <c r="A36" s="650"/>
+      <c r="B36" s="651"/>
       <c r="C36" s="21"/>
-      <c r="D36" s="619"/>
-      <c r="E36" s="619"/>
-      <c r="F36" s="619"/>
-      <c r="G36" s="619"/>
-      <c r="H36" s="619"/>
-      <c r="I36" s="619"/>
+      <c r="D36" s="639"/>
+      <c r="E36" s="639"/>
+      <c r="F36" s="639"/>
+      <c r="G36" s="639"/>
+      <c r="H36" s="639"/>
+      <c r="I36" s="639"/>
       <c r="J36" s="8"/>
       <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="620"/>
-      <c r="B37" s="621"/>
+      <c r="A37" s="650"/>
+      <c r="B37" s="651"/>
       <c r="C37" s="21"/>
-      <c r="D37" s="619"/>
-      <c r="E37" s="619"/>
-      <c r="F37" s="619"/>
-      <c r="G37" s="619"/>
-      <c r="H37" s="619"/>
-      <c r="I37" s="619"/>
+      <c r="D37" s="639"/>
+      <c r="E37" s="639"/>
+      <c r="F37" s="639"/>
+      <c r="G37" s="639"/>
+      <c r="H37" s="639"/>
+      <c r="I37" s="639"/>
       <c r="J37" s="8"/>
       <c r="K37" s="9"/>
     </row>
     <row r="38" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="620"/>
-      <c r="B38" s="621"/>
+      <c r="A38" s="650"/>
+      <c r="B38" s="651"/>
       <c r="C38" s="21"/>
-      <c r="D38" s="619"/>
-      <c r="E38" s="619"/>
-      <c r="F38" s="619"/>
-      <c r="G38" s="619"/>
-      <c r="H38" s="619"/>
-      <c r="I38" s="619"/>
+      <c r="D38" s="639"/>
+      <c r="E38" s="639"/>
+      <c r="F38" s="639"/>
+      <c r="G38" s="639"/>
+      <c r="H38" s="639"/>
+      <c r="I38" s="639"/>
       <c r="J38" s="8"/>
       <c r="K38" s="9"/>
     </row>
     <row r="39" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="620"/>
-      <c r="B39" s="621"/>
+      <c r="A39" s="650"/>
+      <c r="B39" s="651"/>
       <c r="C39" s="21"/>
-      <c r="D39" s="619"/>
-      <c r="E39" s="619"/>
-      <c r="F39" s="619"/>
-      <c r="G39" s="619"/>
-      <c r="H39" s="619"/>
-      <c r="I39" s="619"/>
+      <c r="D39" s="639"/>
+      <c r="E39" s="639"/>
+      <c r="F39" s="639"/>
+      <c r="G39" s="639"/>
+      <c r="H39" s="639"/>
+      <c r="I39" s="639"/>
       <c r="J39" s="8"/>
       <c r="K39" s="9"/>
     </row>
     <row r="40" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="620"/>
-      <c r="B40" s="621"/>
+      <c r="A40" s="650"/>
+      <c r="B40" s="651"/>
       <c r="C40" s="21"/>
-      <c r="D40" s="619"/>
-      <c r="E40" s="619"/>
-      <c r="F40" s="619"/>
-      <c r="G40" s="619"/>
-      <c r="H40" s="619"/>
-      <c r="I40" s="619"/>
+      <c r="D40" s="639"/>
+      <c r="E40" s="639"/>
+      <c r="F40" s="639"/>
+      <c r="G40" s="639"/>
+      <c r="H40" s="639"/>
+      <c r="I40" s="639"/>
       <c r="J40" s="8"/>
       <c r="K40" s="9"/>
     </row>
     <row r="41" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="620"/>
-      <c r="B41" s="621"/>
+      <c r="A41" s="650"/>
+      <c r="B41" s="651"/>
       <c r="C41" s="21"/>
-      <c r="D41" s="619"/>
-      <c r="E41" s="619"/>
-      <c r="F41" s="619"/>
-      <c r="G41" s="619"/>
-      <c r="H41" s="619"/>
-      <c r="I41" s="619"/>
+      <c r="D41" s="639"/>
+      <c r="E41" s="639"/>
+      <c r="F41" s="639"/>
+      <c r="G41" s="639"/>
+      <c r="H41" s="639"/>
+      <c r="I41" s="639"/>
       <c r="J41" s="8"/>
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="620"/>
-      <c r="B42" s="621"/>
+      <c r="A42" s="650"/>
+      <c r="B42" s="651"/>
       <c r="C42" s="21"/>
-      <c r="D42" s="619"/>
-      <c r="E42" s="619"/>
-      <c r="F42" s="619"/>
-      <c r="G42" s="619"/>
-      <c r="H42" s="619"/>
-      <c r="I42" s="619"/>
+      <c r="D42" s="639"/>
+      <c r="E42" s="639"/>
+      <c r="F42" s="639"/>
+      <c r="G42" s="639"/>
+      <c r="H42" s="639"/>
+      <c r="I42" s="639"/>
       <c r="J42" s="8"/>
       <c r="K42" s="9"/>
     </row>
     <row r="43" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="620"/>
-      <c r="B43" s="621"/>
+      <c r="A43" s="650"/>
+      <c r="B43" s="651"/>
       <c r="C43" s="21"/>
-      <c r="D43" s="619"/>
-      <c r="E43" s="619"/>
-      <c r="F43" s="619"/>
-      <c r="G43" s="619"/>
-      <c r="H43" s="619"/>
-      <c r="I43" s="619"/>
+      <c r="D43" s="639"/>
+      <c r="E43" s="639"/>
+      <c r="F43" s="639"/>
+      <c r="G43" s="639"/>
+      <c r="H43" s="639"/>
+      <c r="I43" s="639"/>
       <c r="J43" s="8"/>
       <c r="K43" s="9"/>
     </row>
     <row r="44" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="620"/>
-      <c r="B44" s="621"/>
+      <c r="A44" s="650"/>
+      <c r="B44" s="651"/>
       <c r="C44" s="21"/>
-      <c r="D44" s="619"/>
-      <c r="E44" s="619"/>
-      <c r="F44" s="619"/>
-      <c r="G44" s="619"/>
-      <c r="H44" s="619"/>
-      <c r="I44" s="619"/>
+      <c r="D44" s="639"/>
+      <c r="E44" s="639"/>
+      <c r="F44" s="639"/>
+      <c r="G44" s="639"/>
+      <c r="H44" s="639"/>
+      <c r="I44" s="639"/>
       <c r="J44" s="8"/>
       <c r="K44" s="9"/>
     </row>
     <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="622"/>
-      <c r="B45" s="623"/>
+      <c r="A45" s="661"/>
+      <c r="B45" s="662"/>
       <c r="C45" s="22"/>
-      <c r="D45" s="629"/>
-      <c r="E45" s="629"/>
-      <c r="F45" s="629"/>
-      <c r="G45" s="629"/>
-      <c r="H45" s="629"/>
-      <c r="I45" s="629"/>
+      <c r="D45" s="653"/>
+      <c r="E45" s="653"/>
+      <c r="F45" s="653"/>
+      <c r="G45" s="653"/>
+      <c r="H45" s="653"/>
+      <c r="I45" s="653"/>
       <c r="J45" s="10"/>
       <c r="K45" s="11"/>
     </row>
     <row r="46" spans="1:12" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="630" t="s">
+      <c r="A46" s="668" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="631"/>
-      <c r="C46" s="631"/>
-      <c r="D46" s="631"/>
-      <c r="E46" s="631"/>
-      <c r="F46" s="631"/>
-      <c r="G46" s="631"/>
-      <c r="H46" s="631"/>
-      <c r="I46" s="631"/>
-      <c r="J46" s="632"/>
-      <c r="K46" s="633"/>
+      <c r="B46" s="669"/>
+      <c r="C46" s="669"/>
+      <c r="D46" s="669"/>
+      <c r="E46" s="669"/>
+      <c r="F46" s="669"/>
+      <c r="G46" s="669"/>
+      <c r="H46" s="669"/>
+      <c r="I46" s="669"/>
+      <c r="J46" s="670"/>
+      <c r="K46" s="671"/>
     </row>
     <row r="47" spans="1:12" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="626" t="s">
+      <c r="A47" s="665" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="627"/>
-      <c r="C47" s="628"/>
-      <c r="D47" s="635" t="s">
-        <v>443</v>
-      </c>
-      <c r="E47" s="636"/>
-      <c r="F47" s="636"/>
-      <c r="G47" s="636"/>
-      <c r="H47" s="637"/>
+      <c r="B47" s="666"/>
+      <c r="C47" s="667"/>
+      <c r="D47" s="647"/>
+      <c r="E47" s="648"/>
+      <c r="F47" s="648"/>
+      <c r="G47" s="648"/>
+      <c r="H47" s="649"/>
       <c r="I47" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="J47" s="253" t="s">
-        <v>442</v>
-      </c>
+      <c r="J47" s="253"/>
       <c r="K47" s="258"/>
       <c r="L47" s="254"/>
     </row>
     <row r="48" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="593" t="s">
+      <c r="A48" s="423" t="s">
         <v>401</v>
       </c>
-      <c r="B48" s="593"/>
-      <c r="C48" s="593"/>
-      <c r="D48" s="593"/>
-      <c r="E48" s="593"/>
-      <c r="F48" s="593"/>
-      <c r="G48" s="593"/>
-      <c r="H48" s="593"/>
-      <c r="I48" s="593"/>
-      <c r="J48" s="593"/>
-      <c r="K48" s="593"/>
+      <c r="B48" s="423"/>
+      <c r="C48" s="423"/>
+      <c r="D48" s="423"/>
+      <c r="E48" s="423"/>
+      <c r="F48" s="423"/>
+      <c r="G48" s="423"/>
+      <c r="H48" s="423"/>
+      <c r="I48" s="423"/>
+      <c r="J48" s="423"/>
+      <c r="K48" s="423"/>
       <c r="L48" s="257"/>
     </row>
   </sheetData>
@@ -16754,29 +16541,76 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="117">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:E4"/>
-    <mergeCell ref="G3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D15:F17"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G15:I17"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G25:I25"/>
     <mergeCell ref="A48:K48"/>
     <mergeCell ref="D47:H47"/>
     <mergeCell ref="G43:I43"/>
@@ -16801,76 +16635,29 @@
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B3:E4"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D15:F17"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G15:I17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -16902,294 +16689,280 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="696"/>
-      <c r="B1" s="697"/>
-      <c r="C1" s="697"/>
-      <c r="D1" s="697"/>
-      <c r="E1" s="697"/>
-      <c r="F1" s="697"/>
-      <c r="G1" s="697"/>
-      <c r="H1" s="697"/>
-      <c r="I1" s="697"/>
-      <c r="J1" s="697"/>
-      <c r="K1" s="698"/>
+      <c r="A1" s="706"/>
+      <c r="B1" s="707"/>
+      <c r="C1" s="707"/>
+      <c r="D1" s="707"/>
+      <c r="E1" s="707"/>
+      <c r="F1" s="707"/>
+      <c r="G1" s="707"/>
+      <c r="H1" s="707"/>
+      <c r="I1" s="707"/>
+      <c r="J1" s="707"/>
+      <c r="K1" s="708"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="721" t="s">
+      <c r="A2" s="729" t="s">
         <v>319</v>
       </c>
-      <c r="B2" s="722"/>
-      <c r="C2" s="722"/>
-      <c r="D2" s="722"/>
-      <c r="E2" s="722"/>
-      <c r="F2" s="722"/>
-      <c r="G2" s="722"/>
-      <c r="H2" s="722"/>
-      <c r="I2" s="722"/>
-      <c r="J2" s="722"/>
-      <c r="K2" s="723"/>
+      <c r="B2" s="730"/>
+      <c r="C2" s="730"/>
+      <c r="D2" s="730"/>
+      <c r="E2" s="730"/>
+      <c r="F2" s="730"/>
+      <c r="G2" s="730"/>
+      <c r="H2" s="730"/>
+      <c r="I2" s="730"/>
+      <c r="J2" s="730"/>
+      <c r="K2" s="731"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="705" t="s">
+      <c r="A3" s="712" t="s">
         <v>320</v>
       </c>
-      <c r="B3" s="706" t="s">
+      <c r="B3" s="714" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="706"/>
-      <c r="D3" s="707"/>
-      <c r="E3" s="652" t="s">
+      <c r="C3" s="714"/>
+      <c r="D3" s="715"/>
+      <c r="E3" s="622" t="s">
         <v>322</v>
       </c>
-      <c r="F3" s="653"/>
-      <c r="G3" s="736" t="s">
+      <c r="F3" s="623"/>
+      <c r="G3" s="688" t="s">
         <v>323</v>
       </c>
-      <c r="H3" s="654" t="s">
+      <c r="H3" s="626" t="s">
         <v>324</v>
       </c>
-      <c r="I3" s="716"/>
-      <c r="J3" s="716"/>
-      <c r="K3" s="717"/>
+      <c r="I3" s="724"/>
+      <c r="J3" s="724"/>
+      <c r="K3" s="725"/>
     </row>
     <row r="4" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="695"/>
-      <c r="B4" s="708"/>
-      <c r="C4" s="708"/>
-      <c r="D4" s="709"/>
-      <c r="E4" s="641"/>
-      <c r="F4" s="642"/>
-      <c r="G4" s="737"/>
-      <c r="H4" s="718"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
-      <c r="K4" s="719"/>
+      <c r="A4" s="713"/>
+      <c r="B4" s="716"/>
+      <c r="C4" s="716"/>
+      <c r="D4" s="717"/>
+      <c r="E4" s="624"/>
+      <c r="F4" s="625"/>
+      <c r="G4" s="689"/>
+      <c r="H4" s="726"/>
+      <c r="I4" s="420"/>
+      <c r="J4" s="420"/>
+      <c r="K4" s="727"/>
     </row>
     <row r="5" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
-      <c r="B5" s="724"/>
-      <c r="C5" s="724"/>
-      <c r="D5" s="725"/>
+      <c r="B5" s="732"/>
+      <c r="C5" s="732"/>
+      <c r="D5" s="733"/>
       <c r="E5" s="26" t="s">
         <v>129</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="738"/>
-      <c r="H5" s="720"/>
-      <c r="I5" s="581"/>
-      <c r="J5" s="581"/>
-      <c r="K5" s="582"/>
+      <c r="G5" s="690"/>
+      <c r="H5" s="728"/>
+      <c r="I5" s="482"/>
+      <c r="J5" s="482"/>
+      <c r="K5" s="483"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="713" t="s">
-        <v>438</v>
-      </c>
-      <c r="B6" s="714"/>
-      <c r="C6" s="714"/>
-      <c r="D6" s="715"/>
-      <c r="E6" s="35">
-        <v>45050</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>439</v>
-      </c>
+      <c r="A6" s="721"/>
+      <c r="B6" s="722"/>
+      <c r="C6" s="722"/>
+      <c r="D6" s="723"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="36"/>
-      <c r="H6" s="700"/>
-      <c r="I6" s="701"/>
-      <c r="J6" s="701"/>
-      <c r="K6" s="702"/>
+      <c r="H6" s="691"/>
+      <c r="I6" s="692"/>
+      <c r="J6" s="692"/>
+      <c r="K6" s="693"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="733"/>
-      <c r="B7" s="734"/>
-      <c r="C7" s="734"/>
-      <c r="D7" s="735"/>
+      <c r="A7" s="685"/>
+      <c r="B7" s="686"/>
+      <c r="C7" s="686"/>
+      <c r="D7" s="687"/>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
       <c r="G7" s="36"/>
-      <c r="H7" s="700"/>
-      <c r="I7" s="701"/>
-      <c r="J7" s="701"/>
-      <c r="K7" s="702"/>
+      <c r="H7" s="691"/>
+      <c r="I7" s="692"/>
+      <c r="J7" s="692"/>
+      <c r="K7" s="693"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="733"/>
-      <c r="B8" s="734"/>
-      <c r="C8" s="734"/>
-      <c r="D8" s="735"/>
+      <c r="A8" s="685"/>
+      <c r="B8" s="686"/>
+      <c r="C8" s="686"/>
+      <c r="D8" s="687"/>
       <c r="E8" s="35"/>
       <c r="F8" s="35"/>
       <c r="G8" s="36"/>
-      <c r="H8" s="700"/>
-      <c r="I8" s="701"/>
-      <c r="J8" s="701"/>
-      <c r="K8" s="702"/>
+      <c r="H8" s="691"/>
+      <c r="I8" s="692"/>
+      <c r="J8" s="692"/>
+      <c r="K8" s="693"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="733"/>
-      <c r="B9" s="734"/>
-      <c r="C9" s="734"/>
-      <c r="D9" s="735"/>
+      <c r="A9" s="685"/>
+      <c r="B9" s="686"/>
+      <c r="C9" s="686"/>
+      <c r="D9" s="687"/>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
       <c r="G9" s="36"/>
-      <c r="H9" s="700"/>
-      <c r="I9" s="701"/>
-      <c r="J9" s="701"/>
-      <c r="K9" s="702"/>
+      <c r="H9" s="691"/>
+      <c r="I9" s="692"/>
+      <c r="J9" s="692"/>
+      <c r="K9" s="693"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="733"/>
-      <c r="B10" s="734"/>
-      <c r="C10" s="734"/>
-      <c r="D10" s="735"/>
+      <c r="A10" s="685"/>
+      <c r="B10" s="686"/>
+      <c r="C10" s="686"/>
+      <c r="D10" s="687"/>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
       <c r="G10" s="36"/>
-      <c r="H10" s="700"/>
-      <c r="I10" s="701"/>
-      <c r="J10" s="701"/>
-      <c r="K10" s="702"/>
+      <c r="H10" s="691"/>
+      <c r="I10" s="692"/>
+      <c r="J10" s="692"/>
+      <c r="K10" s="693"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="733"/>
-      <c r="B11" s="734"/>
-      <c r="C11" s="734"/>
-      <c r="D11" s="735"/>
+      <c r="A11" s="685"/>
+      <c r="B11" s="686"/>
+      <c r="C11" s="686"/>
+      <c r="D11" s="687"/>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
       <c r="G11" s="36"/>
-      <c r="H11" s="700"/>
-      <c r="I11" s="701"/>
-      <c r="J11" s="701"/>
-      <c r="K11" s="702"/>
+      <c r="H11" s="691"/>
+      <c r="I11" s="692"/>
+      <c r="J11" s="692"/>
+      <c r="K11" s="693"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="710"/>
-      <c r="B12" s="711"/>
-      <c r="C12" s="711"/>
-      <c r="D12" s="712"/>
+      <c r="A12" s="718"/>
+      <c r="B12" s="719"/>
+      <c r="C12" s="719"/>
+      <c r="D12" s="720"/>
       <c r="E12" s="35"/>
       <c r="F12" s="35"/>
       <c r="G12" s="37"/>
-      <c r="H12" s="672"/>
-      <c r="I12" s="673"/>
-      <c r="J12" s="673"/>
-      <c r="K12" s="674"/>
+      <c r="H12" s="734"/>
+      <c r="I12" s="735"/>
+      <c r="J12" s="735"/>
+      <c r="K12" s="736"/>
     </row>
     <row r="13" spans="1:11" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="643" t="s">
+      <c r="A13" s="654" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="644"/>
-      <c r="C13" s="644"/>
-      <c r="D13" s="644"/>
-      <c r="E13" s="644"/>
-      <c r="F13" s="644"/>
-      <c r="G13" s="644"/>
-      <c r="H13" s="644"/>
-      <c r="I13" s="644"/>
-      <c r="J13" s="644"/>
-      <c r="K13" s="645"/>
+      <c r="B13" s="655"/>
+      <c r="C13" s="655"/>
+      <c r="D13" s="655"/>
+      <c r="E13" s="655"/>
+      <c r="F13" s="655"/>
+      <c r="G13" s="655"/>
+      <c r="H13" s="655"/>
+      <c r="I13" s="655"/>
+      <c r="J13" s="655"/>
+      <c r="K13" s="656"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="675" t="s">
+      <c r="A14" s="737" t="s">
         <v>325</v>
       </c>
-      <c r="B14" s="676"/>
-      <c r="C14" s="676"/>
-      <c r="D14" s="676"/>
-      <c r="E14" s="676"/>
-      <c r="F14" s="676"/>
-      <c r="G14" s="676"/>
-      <c r="H14" s="676"/>
-      <c r="I14" s="676"/>
-      <c r="J14" s="676"/>
-      <c r="K14" s="677"/>
+      <c r="B14" s="738"/>
+      <c r="C14" s="738"/>
+      <c r="D14" s="738"/>
+      <c r="E14" s="738"/>
+      <c r="F14" s="738"/>
+      <c r="G14" s="738"/>
+      <c r="H14" s="738"/>
+      <c r="I14" s="738"/>
+      <c r="J14" s="738"/>
+      <c r="K14" s="739"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="695" t="s">
+      <c r="A15" s="713" t="s">
         <v>326</v>
       </c>
-      <c r="B15" s="639" t="s">
+      <c r="B15" s="643" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="285"/>
-      <c r="D15" s="286"/>
-      <c r="E15" s="639" t="s">
+      <c r="C15" s="420"/>
+      <c r="D15" s="421"/>
+      <c r="E15" s="643" t="s">
         <v>328</v>
       </c>
-      <c r="F15" s="640"/>
-      <c r="G15" s="681" t="s">
+      <c r="F15" s="644"/>
+      <c r="G15" s="740" t="s">
         <v>323</v>
       </c>
-      <c r="H15" s="703" t="s">
+      <c r="H15" s="710" t="s">
         <v>329</v>
       </c>
-      <c r="I15" s="669" t="s">
+      <c r="I15" s="642" t="s">
         <v>330</v>
       </c>
-      <c r="J15" s="285"/>
-      <c r="K15" s="719"/>
+      <c r="J15" s="420"/>
+      <c r="K15" s="727"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="695"/>
-      <c r="B16" s="285"/>
-      <c r="C16" s="285"/>
-      <c r="D16" s="286"/>
-      <c r="E16" s="641"/>
-      <c r="F16" s="642"/>
-      <c r="G16" s="681"/>
-      <c r="H16" s="703"/>
-      <c r="I16" s="718"/>
-      <c r="J16" s="285"/>
-      <c r="K16" s="719"/>
+      <c r="A16" s="713"/>
+      <c r="B16" s="420"/>
+      <c r="C16" s="420"/>
+      <c r="D16" s="421"/>
+      <c r="E16" s="624"/>
+      <c r="F16" s="625"/>
+      <c r="G16" s="740"/>
+      <c r="H16" s="710"/>
+      <c r="I16" s="726"/>
+      <c r="J16" s="420"/>
+      <c r="K16" s="727"/>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
-      <c r="B17" s="581"/>
-      <c r="C17" s="581"/>
-      <c r="D17" s="699"/>
+      <c r="B17" s="482"/>
+      <c r="C17" s="482"/>
+      <c r="D17" s="709"/>
       <c r="E17" s="26" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="682"/>
-      <c r="H17" s="704"/>
-      <c r="I17" s="720"/>
-      <c r="J17" s="581"/>
-      <c r="K17" s="582"/>
+      <c r="G17" s="741"/>
+      <c r="H17" s="711"/>
+      <c r="I17" s="728"/>
+      <c r="J17" s="482"/>
+      <c r="K17" s="483"/>
     </row>
     <row r="18" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="686" t="s">
-        <v>438</v>
-      </c>
-      <c r="B18" s="687"/>
-      <c r="C18" s="687"/>
-      <c r="D18" s="688"/>
-      <c r="E18" s="27">
-        <v>44989</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>440</v>
-      </c>
+      <c r="A18" s="694"/>
+      <c r="B18" s="695"/>
+      <c r="C18" s="695"/>
+      <c r="D18" s="696"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
       <c r="G18" s="29"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="683" t="s">
-        <v>431</v>
-      </c>
-      <c r="J18" s="684"/>
-      <c r="K18" s="685"/>
+      <c r="I18" s="700"/>
+      <c r="J18" s="701"/>
+      <c r="K18" s="702"/>
     </row>
     <row r="19" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="678"/>
-      <c r="B19" s="679"/>
-      <c r="C19" s="679"/>
-      <c r="D19" s="680"/>
+      <c r="A19" s="697"/>
+      <c r="B19" s="698"/>
+      <c r="C19" s="698"/>
+      <c r="D19" s="699"/>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
       <c r="G19" s="29"/>
@@ -17199,10 +16972,10 @@
       <c r="K19" s="32"/>
     </row>
     <row r="20" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="678"/>
-      <c r="B20" s="679"/>
-      <c r="C20" s="679"/>
-      <c r="D20" s="680"/>
+      <c r="A20" s="697"/>
+      <c r="B20" s="698"/>
+      <c r="C20" s="698"/>
+      <c r="D20" s="699"/>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
       <c r="G20" s="29"/>
@@ -17212,10 +16985,10 @@
       <c r="K20" s="32"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="678"/>
-      <c r="B21" s="679"/>
-      <c r="C21" s="679"/>
-      <c r="D21" s="680"/>
+      <c r="A21" s="697"/>
+      <c r="B21" s="698"/>
+      <c r="C21" s="698"/>
+      <c r="D21" s="699"/>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
       <c r="G21" s="29"/>
@@ -17225,10 +16998,10 @@
       <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="678"/>
-      <c r="B22" s="679"/>
-      <c r="C22" s="679"/>
-      <c r="D22" s="680"/>
+      <c r="A22" s="697"/>
+      <c r="B22" s="698"/>
+      <c r="C22" s="698"/>
+      <c r="D22" s="699"/>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
       <c r="G22" s="29"/>
@@ -17238,10 +17011,10 @@
       <c r="K22" s="32"/>
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="678"/>
-      <c r="B23" s="679"/>
-      <c r="C23" s="679"/>
-      <c r="D23" s="680"/>
+      <c r="A23" s="697"/>
+      <c r="B23" s="698"/>
+      <c r="C23" s="698"/>
+      <c r="D23" s="699"/>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
       <c r="G23" s="29"/>
@@ -17251,10 +17024,10 @@
       <c r="K23" s="32"/>
     </row>
     <row r="24" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="678"/>
-      <c r="B24" s="679"/>
-      <c r="C24" s="679"/>
-      <c r="D24" s="680"/>
+      <c r="A24" s="697"/>
+      <c r="B24" s="698"/>
+      <c r="C24" s="698"/>
+      <c r="D24" s="699"/>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
       <c r="G24" s="29"/>
@@ -17264,10 +17037,10 @@
       <c r="K24" s="32"/>
     </row>
     <row r="25" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="678"/>
-      <c r="B25" s="679"/>
-      <c r="C25" s="679"/>
-      <c r="D25" s="680"/>
+      <c r="A25" s="697"/>
+      <c r="B25" s="698"/>
+      <c r="C25" s="698"/>
+      <c r="D25" s="699"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
       <c r="G25" s="29"/>
@@ -17277,43 +17050,43 @@
       <c r="K25" s="32"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="686"/>
-      <c r="B26" s="687"/>
-      <c r="C26" s="687"/>
-      <c r="D26" s="688"/>
+      <c r="A26" s="694"/>
+      <c r="B26" s="695"/>
+      <c r="C26" s="695"/>
+      <c r="D26" s="696"/>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
       <c r="G26" s="29"/>
       <c r="H26" s="28"/>
-      <c r="I26" s="683"/>
-      <c r="J26" s="684"/>
-      <c r="K26" s="685"/>
+      <c r="I26" s="700"/>
+      <c r="J26" s="701"/>
+      <c r="K26" s="702"/>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="686"/>
-      <c r="B27" s="687"/>
-      <c r="C27" s="687"/>
-      <c r="D27" s="688"/>
+      <c r="A27" s="694"/>
+      <c r="B27" s="695"/>
+      <c r="C27" s="695"/>
+      <c r="D27" s="696"/>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
       <c r="G27" s="29"/>
       <c r="H27" s="28"/>
-      <c r="I27" s="683"/>
-      <c r="J27" s="684"/>
-      <c r="K27" s="685"/>
+      <c r="I27" s="700"/>
+      <c r="J27" s="701"/>
+      <c r="K27" s="702"/>
     </row>
     <row r="28" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="686"/>
-      <c r="B28" s="687"/>
-      <c r="C28" s="687"/>
-      <c r="D28" s="688"/>
+      <c r="A28" s="694"/>
+      <c r="B28" s="695"/>
+      <c r="C28" s="695"/>
+      <c r="D28" s="696"/>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
       <c r="G28" s="29"/>
       <c r="H28" s="28"/>
-      <c r="I28" s="683"/>
-      <c r="J28" s="684"/>
-      <c r="K28" s="685"/>
+      <c r="I28" s="700"/>
+      <c r="J28" s="701"/>
+      <c r="K28" s="702"/>
     </row>
     <row r="29" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="202"/>
@@ -17394,86 +17167,86 @@
       <c r="K34" s="32"/>
     </row>
     <row r="35" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="686"/>
-      <c r="B35" s="687"/>
-      <c r="C35" s="687"/>
-      <c r="D35" s="688"/>
+      <c r="A35" s="694"/>
+      <c r="B35" s="695"/>
+      <c r="C35" s="695"/>
+      <c r="D35" s="696"/>
       <c r="E35" s="27"/>
       <c r="F35" s="27"/>
       <c r="G35" s="29"/>
       <c r="H35" s="28"/>
-      <c r="I35" s="683"/>
-      <c r="J35" s="684"/>
-      <c r="K35" s="685"/>
+      <c r="I35" s="700"/>
+      <c r="J35" s="701"/>
+      <c r="K35" s="702"/>
     </row>
     <row r="36" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="686"/>
-      <c r="B36" s="687"/>
-      <c r="C36" s="687"/>
-      <c r="D36" s="688"/>
+      <c r="A36" s="694"/>
+      <c r="B36" s="695"/>
+      <c r="C36" s="695"/>
+      <c r="D36" s="696"/>
       <c r="E36" s="27"/>
       <c r="F36" s="27"/>
       <c r="G36" s="29"/>
       <c r="H36" s="28"/>
-      <c r="I36" s="683"/>
-      <c r="J36" s="684"/>
-      <c r="K36" s="685"/>
+      <c r="I36" s="700"/>
+      <c r="J36" s="701"/>
+      <c r="K36" s="702"/>
     </row>
     <row r="37" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="686"/>
-      <c r="B37" s="687"/>
-      <c r="C37" s="687"/>
-      <c r="D37" s="688"/>
+      <c r="A37" s="694"/>
+      <c r="B37" s="695"/>
+      <c r="C37" s="695"/>
+      <c r="D37" s="696"/>
       <c r="E37" s="27"/>
       <c r="F37" s="27"/>
       <c r="G37" s="29"/>
       <c r="H37" s="28"/>
-      <c r="I37" s="683"/>
-      <c r="J37" s="684"/>
-      <c r="K37" s="685"/>
+      <c r="I37" s="700"/>
+      <c r="J37" s="701"/>
+      <c r="K37" s="702"/>
     </row>
     <row r="38" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="689"/>
-      <c r="B38" s="690"/>
-      <c r="C38" s="690"/>
-      <c r="D38" s="691"/>
+      <c r="A38" s="742"/>
+      <c r="B38" s="743"/>
+      <c r="C38" s="743"/>
+      <c r="D38" s="744"/>
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
       <c r="G38" s="33"/>
       <c r="H38" s="34"/>
-      <c r="I38" s="692"/>
-      <c r="J38" s="693"/>
-      <c r="K38" s="694"/>
+      <c r="I38" s="745"/>
+      <c r="J38" s="746"/>
+      <c r="K38" s="747"/>
     </row>
     <row r="39" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="597" t="s">
+      <c r="A39" s="427" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="598"/>
-      <c r="C39" s="598"/>
-      <c r="D39" s="598"/>
-      <c r="E39" s="598"/>
-      <c r="F39" s="598"/>
-      <c r="G39" s="598"/>
-      <c r="H39" s="598"/>
-      <c r="I39" s="598"/>
-      <c r="J39" s="598"/>
-      <c r="K39" s="599"/>
+      <c r="B39" s="428"/>
+      <c r="C39" s="428"/>
+      <c r="D39" s="428"/>
+      <c r="E39" s="428"/>
+      <c r="F39" s="428"/>
+      <c r="G39" s="428"/>
+      <c r="H39" s="428"/>
+      <c r="I39" s="428"/>
+      <c r="J39" s="428"/>
+      <c r="K39" s="429"/>
     </row>
     <row r="40" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="730" t="s">
+      <c r="A40" s="703" t="s">
         <v>331</v>
       </c>
-      <c r="B40" s="731"/>
-      <c r="C40" s="731"/>
-      <c r="D40" s="731"/>
-      <c r="E40" s="731"/>
-      <c r="F40" s="731"/>
-      <c r="G40" s="731"/>
-      <c r="H40" s="731"/>
-      <c r="I40" s="731"/>
-      <c r="J40" s="731"/>
-      <c r="K40" s="732"/>
+      <c r="B40" s="704"/>
+      <c r="C40" s="704"/>
+      <c r="D40" s="704"/>
+      <c r="E40" s="704"/>
+      <c r="F40" s="704"/>
+      <c r="G40" s="704"/>
+      <c r="H40" s="704"/>
+      <c r="I40" s="704"/>
+      <c r="J40" s="704"/>
+      <c r="K40" s="705"/>
     </row>
     <row r="41" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="144" t="s">
@@ -17485,149 +17258,145 @@
       <c r="C41" s="145" t="s">
         <v>334</v>
       </c>
-      <c r="D41" s="345" t="s">
+      <c r="D41" s="376" t="s">
         <v>335</v>
       </c>
-      <c r="E41" s="345"/>
-      <c r="F41" s="345"/>
-      <c r="G41" s="345"/>
-      <c r="H41" s="739"/>
+      <c r="E41" s="376"/>
+      <c r="F41" s="376"/>
+      <c r="G41" s="376"/>
+      <c r="H41" s="684"/>
       <c r="I41" s="145" t="s">
         <v>336</v>
       </c>
-      <c r="J41" s="345" t="s">
+      <c r="J41" s="376" t="s">
         <v>337</v>
       </c>
-      <c r="K41" s="346"/>
+      <c r="K41" s="377"/>
     </row>
     <row r="42" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="726" t="s">
-        <v>441</v>
-      </c>
-      <c r="B42" s="727"/>
-      <c r="C42" s="728"/>
-      <c r="D42" s="729"/>
-      <c r="E42" s="729"/>
-      <c r="F42" s="729"/>
-      <c r="G42" s="729"/>
-      <c r="H42" s="727"/>
-      <c r="I42" s="728"/>
-      <c r="J42" s="729"/>
-      <c r="K42" s="740"/>
+      <c r="A42" s="679" t="s">
+        <v>403</v>
+      </c>
+      <c r="B42" s="680"/>
+      <c r="C42" s="681"/>
+      <c r="D42" s="682"/>
+      <c r="E42" s="682"/>
+      <c r="F42" s="682"/>
+      <c r="G42" s="682"/>
+      <c r="H42" s="680"/>
+      <c r="I42" s="681"/>
+      <c r="J42" s="682"/>
+      <c r="K42" s="683"/>
     </row>
     <row r="43" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="726"/>
-      <c r="B43" s="727"/>
-      <c r="C43" s="728"/>
-      <c r="D43" s="729"/>
-      <c r="E43" s="729"/>
-      <c r="F43" s="729"/>
-      <c r="G43" s="729"/>
-      <c r="H43" s="727"/>
-      <c r="I43" s="728"/>
-      <c r="J43" s="729"/>
-      <c r="K43" s="740"/>
+      <c r="A43" s="679"/>
+      <c r="B43" s="680"/>
+      <c r="C43" s="681"/>
+      <c r="D43" s="682"/>
+      <c r="E43" s="682"/>
+      <c r="F43" s="682"/>
+      <c r="G43" s="682"/>
+      <c r="H43" s="680"/>
+      <c r="I43" s="681"/>
+      <c r="J43" s="682"/>
+      <c r="K43" s="683"/>
     </row>
     <row r="44" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="726"/>
-      <c r="B44" s="727"/>
-      <c r="C44" s="728"/>
-      <c r="D44" s="729"/>
-      <c r="E44" s="729"/>
-      <c r="F44" s="729"/>
-      <c r="G44" s="729"/>
-      <c r="H44" s="727"/>
-      <c r="I44" s="728"/>
-      <c r="J44" s="729"/>
-      <c r="K44" s="740"/>
+      <c r="A44" s="679"/>
+      <c r="B44" s="680"/>
+      <c r="C44" s="681"/>
+      <c r="D44" s="682"/>
+      <c r="E44" s="682"/>
+      <c r="F44" s="682"/>
+      <c r="G44" s="682"/>
+      <c r="H44" s="680"/>
+      <c r="I44" s="681"/>
+      <c r="J44" s="682"/>
+      <c r="K44" s="683"/>
     </row>
     <row r="45" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="726"/>
-      <c r="B45" s="727"/>
-      <c r="C45" s="728"/>
-      <c r="D45" s="729"/>
-      <c r="E45" s="729"/>
-      <c r="F45" s="729"/>
-      <c r="G45" s="729"/>
-      <c r="H45" s="727"/>
-      <c r="I45" s="728"/>
-      <c r="J45" s="729"/>
-      <c r="K45" s="740"/>
+      <c r="A45" s="679"/>
+      <c r="B45" s="680"/>
+      <c r="C45" s="681"/>
+      <c r="D45" s="682"/>
+      <c r="E45" s="682"/>
+      <c r="F45" s="682"/>
+      <c r="G45" s="682"/>
+      <c r="H45" s="680"/>
+      <c r="I45" s="681"/>
+      <c r="J45" s="682"/>
+      <c r="K45" s="683"/>
     </row>
     <row r="46" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="726"/>
-      <c r="B46" s="727"/>
-      <c r="C46" s="728"/>
-      <c r="D46" s="729"/>
-      <c r="E46" s="729"/>
-      <c r="F46" s="729"/>
-      <c r="G46" s="729"/>
-      <c r="H46" s="727"/>
-      <c r="I46" s="728"/>
-      <c r="J46" s="729"/>
-      <c r="K46" s="740"/>
+      <c r="A46" s="679"/>
+      <c r="B46" s="680"/>
+      <c r="C46" s="681"/>
+      <c r="D46" s="682"/>
+      <c r="E46" s="682"/>
+      <c r="F46" s="682"/>
+      <c r="G46" s="682"/>
+      <c r="H46" s="680"/>
+      <c r="I46" s="681"/>
+      <c r="J46" s="682"/>
+      <c r="K46" s="683"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="726"/>
-      <c r="B47" s="727"/>
-      <c r="C47" s="728"/>
-      <c r="D47" s="729"/>
-      <c r="E47" s="729"/>
-      <c r="F47" s="729"/>
-      <c r="G47" s="729"/>
-      <c r="H47" s="727"/>
-      <c r="I47" s="728"/>
-      <c r="J47" s="729"/>
-      <c r="K47" s="740"/>
+      <c r="A47" s="679"/>
+      <c r="B47" s="680"/>
+      <c r="C47" s="681"/>
+      <c r="D47" s="682"/>
+      <c r="E47" s="682"/>
+      <c r="F47" s="682"/>
+      <c r="G47" s="682"/>
+      <c r="H47" s="680"/>
+      <c r="I47" s="681"/>
+      <c r="J47" s="682"/>
+      <c r="K47" s="683"/>
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="726"/>
-      <c r="B48" s="727"/>
-      <c r="C48" s="728"/>
-      <c r="D48" s="729"/>
-      <c r="E48" s="729"/>
-      <c r="F48" s="729"/>
-      <c r="G48" s="729"/>
-      <c r="H48" s="727"/>
-      <c r="I48" s="728"/>
-      <c r="J48" s="729"/>
-      <c r="K48" s="740"/>
+      <c r="A48" s="679"/>
+      <c r="B48" s="680"/>
+      <c r="C48" s="681"/>
+      <c r="D48" s="682"/>
+      <c r="E48" s="682"/>
+      <c r="F48" s="682"/>
+      <c r="G48" s="682"/>
+      <c r="H48" s="680"/>
+      <c r="I48" s="681"/>
+      <c r="J48" s="682"/>
+      <c r="K48" s="683"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="597" t="s">
+      <c r="A49" s="427" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="598"/>
-      <c r="C49" s="598"/>
-      <c r="D49" s="598"/>
-      <c r="E49" s="598"/>
-      <c r="F49" s="598"/>
-      <c r="G49" s="598"/>
-      <c r="H49" s="598"/>
-      <c r="I49" s="598"/>
-      <c r="J49" s="598"/>
-      <c r="K49" s="645"/>
+      <c r="B49" s="428"/>
+      <c r="C49" s="428"/>
+      <c r="D49" s="428"/>
+      <c r="E49" s="428"/>
+      <c r="F49" s="428"/>
+      <c r="G49" s="428"/>
+      <c r="H49" s="428"/>
+      <c r="I49" s="428"/>
+      <c r="J49" s="428"/>
+      <c r="K49" s="656"/>
     </row>
     <row r="50" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="626" t="s">
+      <c r="A50" s="665" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="628"/>
-      <c r="C50" s="635" t="s">
-        <v>443</v>
-      </c>
-      <c r="D50" s="743"/>
-      <c r="E50" s="743"/>
-      <c r="F50" s="744"/>
-      <c r="G50" s="741" t="s">
+      <c r="B50" s="667"/>
+      <c r="C50" s="647"/>
+      <c r="D50" s="674"/>
+      <c r="E50" s="674"/>
+      <c r="F50" s="675"/>
+      <c r="G50" s="672" t="s">
         <v>144</v>
       </c>
-      <c r="H50" s="742"/>
-      <c r="I50" s="745" t="s">
-        <v>442</v>
-      </c>
-      <c r="J50" s="746"/>
-      <c r="K50" s="747"/>
+      <c r="H50" s="673"/>
+      <c r="I50" s="676"/>
+      <c r="J50" s="677"/>
+      <c r="K50" s="678"/>
       <c r="L50" s="255"/>
       <c r="M50" s="255"/>
     </row>
@@ -17648,6 +17417,73 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="83">
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B15:D17"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="H3:K5"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I15:K17"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="C48:H48"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="C45:H45"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="I44:K44"/>
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="I50:K50"/>
@@ -17664,73 +17500,6 @@
     <mergeCell ref="I46:K46"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="I47:K47"/>
-    <mergeCell ref="C48:H48"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="C45:H45"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B15:D17"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="H3:K5"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I15:K17"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -17763,35 +17532,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="291"/>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="293"/>
+      <c r="A1" s="401"/>
+      <c r="B1" s="402"/>
+      <c r="C1" s="402"/>
+      <c r="D1" s="402"/>
+      <c r="E1" s="402"/>
+      <c r="F1" s="402"/>
+      <c r="G1" s="402"/>
+      <c r="H1" s="402"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
+      <c r="K1" s="402"/>
+      <c r="L1" s="402"/>
+      <c r="M1" s="403"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="316" t="s">
+      <c r="A2" s="378" t="s">
         <v>338</v>
       </c>
-      <c r="B2" s="317"/>
-      <c r="C2" s="296" t="s">
+      <c r="B2" s="379"/>
+      <c r="C2" s="406" t="s">
         <v>339</v>
       </c>
-      <c r="D2" s="296"/>
-      <c r="E2" s="296"/>
-      <c r="F2" s="297"/>
+      <c r="D2" s="406"/>
+      <c r="E2" s="406"/>
+      <c r="F2" s="407"/>
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
-      <c r="I2" s="294"/>
-      <c r="J2" s="294"/>
+      <c r="I2" s="404"/>
+      <c r="J2" s="404"/>
       <c r="K2" s="39"/>
       <c r="L2" s="39"/>
       <c r="M2" s="40"/>
@@ -17799,16 +17568,16 @@
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="300" t="s">
+      <c r="C3" s="394" t="s">
         <v>340</v>
       </c>
-      <c r="D3" s="300"/>
-      <c r="E3" s="300"/>
-      <c r="F3" s="301"/>
+      <c r="D3" s="394"/>
+      <c r="E3" s="394"/>
+      <c r="F3" s="395"/>
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
-      <c r="I3" s="295"/>
-      <c r="J3" s="295"/>
+      <c r="I3" s="405"/>
+      <c r="J3" s="405"/>
       <c r="K3" s="44"/>
       <c r="L3" s="44"/>
       <c r="M3" s="45"/>
@@ -17816,42 +17585,42 @@
     <row r="4" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="300" t="s">
+      <c r="C4" s="394" t="s">
         <v>341</v>
       </c>
-      <c r="D4" s="300"/>
-      <c r="E4" s="300"/>
-      <c r="F4" s="301"/>
+      <c r="D4" s="394"/>
+      <c r="E4" s="394"/>
+      <c r="F4" s="395"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41"/>
       <c r="B5" s="42"/>
-      <c r="C5" s="300"/>
-      <c r="D5" s="300"/>
-      <c r="E5" s="300"/>
-      <c r="F5" s="301"/>
-      <c r="G5" s="288"/>
-      <c r="H5" s="288"/>
-      <c r="I5" s="288"/>
-      <c r="J5" s="288"/>
-      <c r="K5" s="288"/>
-      <c r="L5" s="288"/>
+      <c r="C5" s="394"/>
+      <c r="D5" s="394"/>
+      <c r="E5" s="394"/>
+      <c r="F5" s="395"/>
+      <c r="G5" s="307"/>
+      <c r="H5" s="307"/>
+      <c r="I5" s="307"/>
+      <c r="J5" s="307"/>
+      <c r="K5" s="307"/>
+      <c r="L5" s="307"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
-      <c r="C6" s="300" t="s">
+      <c r="C6" s="394" t="s">
         <v>342</v>
       </c>
-      <c r="D6" s="300"/>
-      <c r="E6" s="300"/>
-      <c r="F6" s="301"/>
-      <c r="I6" s="322"/>
-      <c r="J6" s="322"/>
-      <c r="K6" s="322"/>
-      <c r="L6" s="322"/>
+      <c r="D6" s="394"/>
+      <c r="E6" s="394"/>
+      <c r="F6" s="395"/>
+      <c r="I6" s="400"/>
+      <c r="J6" s="400"/>
+      <c r="K6" s="400"/>
+      <c r="L6" s="400"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -17870,12 +17639,12 @@
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="42"/>
-      <c r="C8" s="300" t="s">
+      <c r="C8" s="394" t="s">
         <v>343</v>
       </c>
-      <c r="D8" s="300"/>
-      <c r="E8" s="300"/>
-      <c r="F8" s="301"/>
+      <c r="D8" s="394"/>
+      <c r="E8" s="394"/>
+      <c r="F8" s="395"/>
       <c r="M8" s="46"/>
     </row>
     <row r="9" spans="1:13" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -17890,61 +17659,61 @@
     <row r="10" spans="1:13" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="41"/>
       <c r="B10" s="42"/>
-      <c r="C10" s="300"/>
-      <c r="D10" s="300"/>
-      <c r="E10" s="300"/>
-      <c r="F10" s="301"/>
-      <c r="G10" s="288" t="s">
+      <c r="C10" s="394"/>
+      <c r="D10" s="394"/>
+      <c r="E10" s="394"/>
+      <c r="F10" s="395"/>
+      <c r="G10" s="307" t="s">
         <v>344</v>
       </c>
-      <c r="H10" s="288"/>
-      <c r="I10" s="288"/>
-      <c r="J10" s="288"/>
-      <c r="K10" s="288"/>
-      <c r="L10" s="288"/>
+      <c r="H10" s="307"/>
+      <c r="I10" s="307"/>
+      <c r="J10" s="307"/>
+      <c r="K10" s="307"/>
+      <c r="L10" s="307"/>
       <c r="M10" s="93"/>
     </row>
     <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41"/>
       <c r="B11" s="42"/>
-      <c r="C11" s="300"/>
-      <c r="D11" s="300"/>
-      <c r="E11" s="300"/>
-      <c r="F11" s="301"/>
+      <c r="C11" s="394"/>
+      <c r="D11" s="394"/>
+      <c r="E11" s="394"/>
+      <c r="F11" s="395"/>
       <c r="G11" s="152"/>
       <c r="H11" s="153"/>
-      <c r="I11" s="320"/>
-      <c r="J11" s="320"/>
-      <c r="K11" s="320"/>
-      <c r="L11" s="320"/>
+      <c r="I11" s="398"/>
+      <c r="J11" s="398"/>
+      <c r="K11" s="398"/>
+      <c r="L11" s="398"/>
       <c r="M11" s="93"/>
     </row>
     <row r="12" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="47"/>
       <c r="B12" s="48"/>
-      <c r="C12" s="318"/>
-      <c r="D12" s="318"/>
-      <c r="E12" s="318"/>
-      <c r="F12" s="319"/>
+      <c r="C12" s="396"/>
+      <c r="D12" s="396"/>
+      <c r="E12" s="396"/>
+      <c r="F12" s="397"/>
       <c r="G12" s="153"/>
       <c r="H12" s="153"/>
-      <c r="I12" s="321"/>
-      <c r="J12" s="321"/>
-      <c r="K12" s="321"/>
-      <c r="L12" s="321"/>
+      <c r="I12" s="399"/>
+      <c r="J12" s="399"/>
+      <c r="K12" s="399"/>
+      <c r="L12" s="399"/>
       <c r="M12" s="131"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="282" t="s">
+      <c r="A13" s="418" t="s">
         <v>345</v>
       </c>
-      <c r="B13" s="283"/>
-      <c r="C13" s="284" t="s">
+      <c r="B13" s="419"/>
+      <c r="C13" s="414" t="s">
         <v>346</v>
       </c>
-      <c r="D13" s="284"/>
-      <c r="E13" s="285"/>
-      <c r="F13" s="286"/>
+      <c r="D13" s="414"/>
+      <c r="E13" s="420"/>
+      <c r="F13" s="421"/>
       <c r="G13" s="49"/>
       <c r="H13" s="49"/>
       <c r="I13" s="49"/>
@@ -17956,48 +17725,48 @@
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
       <c r="B14" s="65"/>
-      <c r="C14" s="284"/>
-      <c r="D14" s="284"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="286"/>
-      <c r="G14" s="287" t="s">
+      <c r="C14" s="414"/>
+      <c r="D14" s="414"/>
+      <c r="E14" s="420"/>
+      <c r="F14" s="421"/>
+      <c r="G14" s="306" t="s">
         <v>344</v>
       </c>
-      <c r="H14" s="288"/>
-      <c r="I14" s="288"/>
-      <c r="J14" s="288"/>
-      <c r="K14" s="288"/>
-      <c r="L14" s="288"/>
+      <c r="H14" s="307"/>
+      <c r="I14" s="307"/>
+      <c r="J14" s="307"/>
+      <c r="K14" s="307"/>
+      <c r="L14" s="307"/>
       <c r="M14" s="130"/>
     </row>
     <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64"/>
       <c r="B15" s="65"/>
-      <c r="C15" s="284"/>
-      <c r="D15" s="284"/>
-      <c r="E15" s="285"/>
-      <c r="F15" s="286"/>
+      <c r="C15" s="414"/>
+      <c r="D15" s="414"/>
+      <c r="E15" s="420"/>
+      <c r="F15" s="421"/>
       <c r="G15" s="43"/>
       <c r="H15" s="270"/>
-      <c r="I15" s="289"/>
-      <c r="J15" s="289"/>
-      <c r="K15" s="289"/>
-      <c r="L15" s="289"/>
+      <c r="I15" s="422"/>
+      <c r="J15" s="422"/>
+      <c r="K15" s="422"/>
+      <c r="L15" s="422"/>
       <c r="M15" s="130"/>
     </row>
     <row r="16" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="51"/>
       <c r="B16" s="52"/>
-      <c r="C16" s="285"/>
-      <c r="D16" s="285"/>
-      <c r="E16" s="285"/>
-      <c r="F16" s="286"/>
+      <c r="C16" s="420"/>
+      <c r="D16" s="420"/>
+      <c r="E16" s="420"/>
+      <c r="F16" s="421"/>
       <c r="G16" s="127"/>
       <c r="H16" s="260"/>
-      <c r="I16" s="290"/>
-      <c r="J16" s="290"/>
-      <c r="K16" s="290"/>
-      <c r="L16" s="290"/>
+      <c r="I16" s="411"/>
+      <c r="J16" s="411"/>
+      <c r="K16" s="411"/>
+      <c r="L16" s="411"/>
       <c r="M16" s="128"/>
     </row>
     <row r="17" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18018,12 +17787,12 @@
     <row r="18" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53"/>
       <c r="B18" s="54"/>
-      <c r="C18" s="417" t="s">
+      <c r="C18" s="309" t="s">
         <v>347</v>
       </c>
-      <c r="D18" s="417"/>
-      <c r="E18" s="418"/>
-      <c r="F18" s="419"/>
+      <c r="D18" s="309"/>
+      <c r="E18" s="310"/>
+      <c r="F18" s="311"/>
       <c r="G18" s="58"/>
       <c r="H18" s="58"/>
       <c r="I18" s="58"/>
@@ -18035,32 +17804,32 @@
     <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="417"/>
-      <c r="D19" s="417"/>
-      <c r="E19" s="418"/>
-      <c r="F19" s="419"/>
-      <c r="G19" s="287" t="s">
+      <c r="C19" s="309"/>
+      <c r="D19" s="309"/>
+      <c r="E19" s="310"/>
+      <c r="F19" s="311"/>
+      <c r="G19" s="306" t="s">
         <v>344</v>
       </c>
-      <c r="H19" s="288"/>
-      <c r="I19" s="288"/>
-      <c r="J19" s="288"/>
-      <c r="K19" s="288"/>
-      <c r="L19" s="288"/>
+      <c r="H19" s="307"/>
+      <c r="I19" s="307"/>
+      <c r="J19" s="307"/>
+      <c r="K19" s="307"/>
+      <c r="L19" s="307"/>
       <c r="M19" s="59"/>
     </row>
     <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53"/>
       <c r="B20" s="54"/>
-      <c r="C20" s="417"/>
-      <c r="D20" s="417"/>
-      <c r="E20" s="418"/>
-      <c r="F20" s="419"/>
+      <c r="C20" s="309"/>
+      <c r="D20" s="309"/>
+      <c r="E20" s="310"/>
+      <c r="F20" s="311"/>
       <c r="G20" s="58"/>
-      <c r="H20" s="395" t="s">
+      <c r="H20" s="282" t="s">
         <v>348</v>
       </c>
-      <c r="I20" s="395"/>
+      <c r="I20" s="282"/>
       <c r="J20" s="271"/>
       <c r="K20" s="272"/>
       <c r="L20" s="132"/>
@@ -18069,15 +17838,15 @@
     <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53"/>
       <c r="B21" s="54"/>
-      <c r="C21" s="417"/>
-      <c r="D21" s="417"/>
-      <c r="E21" s="418"/>
-      <c r="F21" s="419"/>
-      <c r="G21" s="396" t="s">
+      <c r="C21" s="309"/>
+      <c r="D21" s="309"/>
+      <c r="E21" s="310"/>
+      <c r="F21" s="311"/>
+      <c r="G21" s="283" t="s">
         <v>349</v>
       </c>
-      <c r="H21" s="397"/>
-      <c r="I21" s="397"/>
+      <c r="H21" s="284"/>
+      <c r="I21" s="284"/>
       <c r="J21" s="271"/>
       <c r="K21" s="273"/>
       <c r="L21" s="132"/>
@@ -18086,31 +17855,31 @@
     <row r="22" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="420"/>
-      <c r="D22" s="420"/>
-      <c r="E22" s="420"/>
-      <c r="F22" s="421"/>
+      <c r="C22" s="312"/>
+      <c r="D22" s="312"/>
+      <c r="E22" s="312"/>
+      <c r="F22" s="313"/>
       <c r="G22" s="127" t="s">
         <v>350</v>
       </c>
       <c r="H22" s="260"/>
-      <c r="I22" s="422"/>
-      <c r="J22" s="422"/>
-      <c r="K22" s="422"/>
+      <c r="I22" s="314"/>
+      <c r="J22" s="314"/>
+      <c r="K22" s="314"/>
       <c r="L22" s="133"/>
       <c r="M22" s="128"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="323" t="s">
+      <c r="A23" s="302" t="s">
         <v>351</v>
       </c>
-      <c r="B23" s="324"/>
-      <c r="C23" s="312" t="s">
+      <c r="B23" s="303"/>
+      <c r="C23" s="316" t="s">
         <v>352</v>
       </c>
-      <c r="D23" s="312"/>
-      <c r="E23" s="312"/>
-      <c r="F23" s="313"/>
+      <c r="D23" s="316"/>
+      <c r="E23" s="316"/>
+      <c r="F23" s="317"/>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49"/>
@@ -18122,61 +17891,61 @@
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="51"/>
       <c r="B24" s="52"/>
-      <c r="C24" s="303"/>
-      <c r="D24" s="303"/>
-      <c r="E24" s="303"/>
-      <c r="F24" s="302"/>
-      <c r="G24" s="287" t="s">
+      <c r="C24" s="318"/>
+      <c r="D24" s="318"/>
+      <c r="E24" s="318"/>
+      <c r="F24" s="319"/>
+      <c r="G24" s="306" t="s">
         <v>344</v>
       </c>
-      <c r="H24" s="288"/>
-      <c r="I24" s="288"/>
-      <c r="J24" s="288"/>
-      <c r="K24" s="288"/>
-      <c r="L24" s="288"/>
+      <c r="H24" s="307"/>
+      <c r="I24" s="307"/>
+      <c r="J24" s="307"/>
+      <c r="K24" s="307"/>
+      <c r="L24" s="307"/>
       <c r="M24" s="126"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="51"/>
       <c r="B25" s="52"/>
-      <c r="C25" s="303"/>
-      <c r="D25" s="303"/>
-      <c r="E25" s="303"/>
-      <c r="F25" s="302"/>
+      <c r="C25" s="318"/>
+      <c r="D25" s="318"/>
+      <c r="E25" s="318"/>
+      <c r="F25" s="319"/>
       <c r="G25" s="125"/>
       <c r="H25" s="260"/>
-      <c r="I25" s="311"/>
-      <c r="J25" s="311"/>
-      <c r="K25" s="311"/>
-      <c r="L25" s="311"/>
+      <c r="I25" s="315"/>
+      <c r="J25" s="315"/>
+      <c r="K25" s="315"/>
+      <c r="L25" s="315"/>
       <c r="M25" s="126"/>
     </row>
     <row r="26" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="62"/>
       <c r="B26" s="63"/>
-      <c r="C26" s="314"/>
-      <c r="D26" s="314"/>
-      <c r="E26" s="314"/>
-      <c r="F26" s="315"/>
+      <c r="C26" s="320"/>
+      <c r="D26" s="320"/>
+      <c r="E26" s="320"/>
+      <c r="F26" s="321"/>
       <c r="G26" s="127"/>
       <c r="H26" s="260"/>
-      <c r="I26" s="290"/>
-      <c r="J26" s="290"/>
-      <c r="K26" s="290"/>
-      <c r="L26" s="290"/>
+      <c r="I26" s="411"/>
+      <c r="J26" s="411"/>
+      <c r="K26" s="411"/>
+      <c r="L26" s="411"/>
       <c r="M26" s="128"/>
     </row>
     <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="323" t="s">
+      <c r="A27" s="302" t="s">
         <v>353</v>
       </c>
-      <c r="B27" s="324"/>
-      <c r="C27" s="312" t="s">
+      <c r="B27" s="303"/>
+      <c r="C27" s="316" t="s">
         <v>354</v>
       </c>
-      <c r="D27" s="312"/>
-      <c r="E27" s="312"/>
-      <c r="F27" s="313"/>
+      <c r="D27" s="316"/>
+      <c r="E27" s="316"/>
+      <c r="F27" s="317"/>
       <c r="G27" s="49"/>
       <c r="H27" s="49"/>
       <c r="I27" s="49"/>
@@ -18188,41 +17957,41 @@
     <row r="28" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="51"/>
       <c r="B28" s="52"/>
-      <c r="C28" s="303"/>
-      <c r="D28" s="303"/>
-      <c r="E28" s="303"/>
-      <c r="F28" s="302"/>
-      <c r="G28" s="287" t="s">
+      <c r="C28" s="318"/>
+      <c r="D28" s="318"/>
+      <c r="E28" s="318"/>
+      <c r="F28" s="319"/>
+      <c r="G28" s="306" t="s">
         <v>344</v>
       </c>
-      <c r="H28" s="288"/>
-      <c r="I28" s="288"/>
-      <c r="J28" s="288"/>
-      <c r="K28" s="288"/>
-      <c r="L28" s="288"/>
+      <c r="H28" s="307"/>
+      <c r="I28" s="307"/>
+      <c r="J28" s="307"/>
+      <c r="K28" s="307"/>
+      <c r="L28" s="307"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="51"/>
       <c r="B29" s="52"/>
-      <c r="C29" s="303"/>
-      <c r="D29" s="303"/>
-      <c r="E29" s="303"/>
-      <c r="F29" s="302"/>
+      <c r="C29" s="318"/>
+      <c r="D29" s="318"/>
+      <c r="E29" s="318"/>
+      <c r="F29" s="319"/>
       <c r="H29" s="189"/>
-      <c r="I29" s="311"/>
-      <c r="J29" s="311"/>
-      <c r="K29" s="311"/>
-      <c r="L29" s="311"/>
+      <c r="I29" s="315"/>
+      <c r="J29" s="315"/>
+      <c r="K29" s="315"/>
+      <c r="L29" s="315"/>
       <c r="M29" s="126"/>
     </row>
     <row r="30" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="62"/>
       <c r="B30" s="63"/>
-      <c r="C30" s="314"/>
-      <c r="D30" s="314"/>
-      <c r="E30" s="314"/>
-      <c r="F30" s="315"/>
+      <c r="C30" s="320"/>
+      <c r="D30" s="320"/>
+      <c r="E30" s="320"/>
+      <c r="F30" s="321"/>
       <c r="G30" s="147"/>
       <c r="H30" s="262"/>
       <c r="I30" s="189"/>
@@ -18232,16 +18001,16 @@
       <c r="M30" s="128"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="323" t="s">
+      <c r="A31" s="302" t="s">
         <v>355</v>
       </c>
-      <c r="B31" s="324"/>
-      <c r="C31" s="312" t="s">
+      <c r="B31" s="303"/>
+      <c r="C31" s="316" t="s">
         <v>356</v>
       </c>
-      <c r="D31" s="312"/>
-      <c r="E31" s="312"/>
-      <c r="F31" s="313"/>
+      <c r="D31" s="316"/>
+      <c r="E31" s="316"/>
+      <c r="F31" s="317"/>
       <c r="G31" s="49"/>
       <c r="H31" s="49"/>
       <c r="I31" s="49"/>
@@ -18253,18 +18022,18 @@
     <row r="32" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="51"/>
       <c r="B32" s="52"/>
-      <c r="C32" s="303"/>
-      <c r="D32" s="303"/>
-      <c r="E32" s="303"/>
-      <c r="F32" s="302"/>
-      <c r="G32" s="362" t="s">
+      <c r="C32" s="318"/>
+      <c r="D32" s="318"/>
+      <c r="E32" s="318"/>
+      <c r="F32" s="319"/>
+      <c r="G32" s="354" t="s">
         <v>357</v>
       </c>
-      <c r="H32" s="363"/>
-      <c r="I32" s="363"/>
-      <c r="J32" s="363"/>
-      <c r="K32" s="325"/>
-      <c r="L32" s="325"/>
+      <c r="H32" s="355"/>
+      <c r="I32" s="355"/>
+      <c r="J32" s="355"/>
+      <c r="K32" s="353"/>
+      <c r="L32" s="353"/>
       <c r="M32" s="126"/>
     </row>
     <row r="33" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18285,44 +18054,44 @@
     <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="51"/>
       <c r="B34" s="52"/>
-      <c r="C34" s="303" t="s">
+      <c r="C34" s="318" t="s">
         <v>358</v>
       </c>
-      <c r="D34" s="303"/>
-      <c r="E34" s="303"/>
-      <c r="F34" s="302"/>
+      <c r="D34" s="318"/>
+      <c r="E34" s="318"/>
+      <c r="F34" s="319"/>
       <c r="G34" s="125"/>
       <c r="H34" s="261"/>
-      <c r="I34" s="361"/>
-      <c r="J34" s="361"/>
-      <c r="K34" s="361"/>
-      <c r="L34" s="361"/>
+      <c r="I34" s="352"/>
+      <c r="J34" s="352"/>
+      <c r="K34" s="352"/>
+      <c r="L34" s="352"/>
       <c r="M34" s="126"/>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51"/>
       <c r="B35" s="52"/>
-      <c r="C35" s="303"/>
-      <c r="D35" s="303"/>
-      <c r="E35" s="303"/>
-      <c r="F35" s="302"/>
-      <c r="G35" s="362" t="s">
+      <c r="C35" s="318"/>
+      <c r="D35" s="318"/>
+      <c r="E35" s="318"/>
+      <c r="F35" s="319"/>
+      <c r="G35" s="354" t="s">
         <v>357</v>
       </c>
-      <c r="H35" s="363"/>
-      <c r="I35" s="363"/>
-      <c r="J35" s="363"/>
-      <c r="K35" s="325"/>
-      <c r="L35" s="325"/>
+      <c r="H35" s="355"/>
+      <c r="I35" s="355"/>
+      <c r="J35" s="355"/>
+      <c r="K35" s="353"/>
+      <c r="L35" s="353"/>
       <c r="M35" s="126"/>
     </row>
     <row r="36" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="62"/>
       <c r="B36" s="63"/>
-      <c r="C36" s="314"/>
-      <c r="D36" s="314"/>
-      <c r="E36" s="314"/>
-      <c r="F36" s="315"/>
+      <c r="C36" s="320"/>
+      <c r="D36" s="320"/>
+      <c r="E36" s="320"/>
+      <c r="F36" s="321"/>
       <c r="G36" s="129"/>
       <c r="H36" s="73"/>
       <c r="I36" s="120"/>
@@ -18331,16 +18100,16 @@
       <c r="M36" s="128"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="323" t="s">
+      <c r="A37" s="302" t="s">
         <v>359</v>
       </c>
-      <c r="B37" s="324"/>
-      <c r="C37" s="306" t="s">
+      <c r="B37" s="303"/>
+      <c r="C37" s="412" t="s">
         <v>360</v>
       </c>
-      <c r="D37" s="306"/>
-      <c r="E37" s="306"/>
-      <c r="F37" s="307"/>
+      <c r="D37" s="412"/>
+      <c r="E37" s="412"/>
+      <c r="F37" s="413"/>
       <c r="G37" s="49"/>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
@@ -18352,61 +18121,61 @@
     <row r="38" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="51"/>
       <c r="B38" s="52"/>
-      <c r="C38" s="284"/>
-      <c r="D38" s="284"/>
-      <c r="E38" s="284"/>
-      <c r="F38" s="308"/>
-      <c r="G38" s="287" t="s">
+      <c r="C38" s="414"/>
+      <c r="D38" s="414"/>
+      <c r="E38" s="414"/>
+      <c r="F38" s="415"/>
+      <c r="G38" s="306" t="s">
         <v>361</v>
       </c>
-      <c r="H38" s="288"/>
-      <c r="I38" s="288"/>
-      <c r="J38" s="288"/>
-      <c r="K38" s="288"/>
-      <c r="L38" s="288"/>
-      <c r="M38" s="416"/>
+      <c r="H38" s="307"/>
+      <c r="I38" s="307"/>
+      <c r="J38" s="307"/>
+      <c r="K38" s="307"/>
+      <c r="L38" s="307"/>
+      <c r="M38" s="308"/>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="51"/>
       <c r="B39" s="52"/>
-      <c r="C39" s="284"/>
-      <c r="D39" s="284"/>
-      <c r="E39" s="284"/>
-      <c r="F39" s="308"/>
+      <c r="C39" s="414"/>
+      <c r="D39" s="414"/>
+      <c r="E39" s="414"/>
+      <c r="F39" s="415"/>
       <c r="G39" s="125"/>
       <c r="H39" s="260"/>
-      <c r="I39" s="311"/>
-      <c r="J39" s="311"/>
-      <c r="K39" s="311"/>
-      <c r="L39" s="311"/>
+      <c r="I39" s="315"/>
+      <c r="J39" s="315"/>
+      <c r="K39" s="315"/>
+      <c r="L39" s="315"/>
       <c r="M39" s="126"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="62"/>
       <c r="B40" s="63"/>
-      <c r="C40" s="309"/>
-      <c r="D40" s="309"/>
-      <c r="E40" s="309"/>
-      <c r="F40" s="310"/>
+      <c r="C40" s="416"/>
+      <c r="D40" s="416"/>
+      <c r="E40" s="416"/>
+      <c r="F40" s="417"/>
       <c r="G40" s="127"/>
       <c r="H40" s="260"/>
-      <c r="I40" s="290"/>
-      <c r="J40" s="290"/>
-      <c r="K40" s="290"/>
-      <c r="L40" s="290"/>
+      <c r="I40" s="411"/>
+      <c r="J40" s="411"/>
+      <c r="K40" s="411"/>
+      <c r="L40" s="411"/>
       <c r="M40" s="128"/>
     </row>
     <row r="41" spans="1:14" ht="41.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="304" t="s">
+      <c r="A41" s="409" t="s">
         <v>362</v>
       </c>
-      <c r="B41" s="305"/>
-      <c r="C41" s="303" t="s">
+      <c r="B41" s="410"/>
+      <c r="C41" s="318" t="s">
         <v>363</v>
       </c>
-      <c r="D41" s="303"/>
-      <c r="E41" s="303"/>
-      <c r="F41" s="302"/>
+      <c r="D41" s="318"/>
+      <c r="E41" s="318"/>
+      <c r="F41" s="319"/>
       <c r="G41" s="49"/>
       <c r="H41" s="49"/>
       <c r="I41" s="68"/>
@@ -18418,10 +18187,10 @@
     <row r="42" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="66"/>
       <c r="B42" s="67"/>
-      <c r="C42" s="303"/>
-      <c r="D42" s="303"/>
-      <c r="E42" s="303"/>
-      <c r="F42" s="302"/>
+      <c r="C42" s="318"/>
+      <c r="D42" s="318"/>
+      <c r="E42" s="318"/>
+      <c r="F42" s="319"/>
       <c r="G42" s="71"/>
       <c r="H42" s="71"/>
       <c r="I42" s="71"/>
@@ -18435,21 +18204,21 @@
         <v>364</v>
       </c>
       <c r="B43" s="67"/>
-      <c r="C43" s="303" t="s">
+      <c r="C43" s="318" t="s">
         <v>365</v>
       </c>
-      <c r="D43" s="303"/>
-      <c r="E43" s="303"/>
-      <c r="F43" s="302"/>
+      <c r="D43" s="318"/>
+      <c r="E43" s="318"/>
+      <c r="F43" s="319"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="66"/>
       <c r="B44" s="67"/>
-      <c r="C44" s="303"/>
-      <c r="D44" s="303"/>
-      <c r="E44" s="303"/>
-      <c r="F44" s="302"/>
+      <c r="C44" s="318"/>
+      <c r="D44" s="318"/>
+      <c r="E44" s="318"/>
+      <c r="F44" s="319"/>
       <c r="G44" s="199" t="s">
         <v>366</v>
       </c>
@@ -18465,21 +18234,21 @@
         <v>367</v>
       </c>
       <c r="B45" s="67"/>
-      <c r="C45" s="302" t="s">
+      <c r="C45" s="319" t="s">
         <v>368</v>
       </c>
-      <c r="D45" s="302"/>
-      <c r="E45" s="302"/>
-      <c r="F45" s="302"/>
+      <c r="D45" s="319"/>
+      <c r="E45" s="319"/>
+      <c r="F45" s="319"/>
       <c r="M45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="66"/>
       <c r="B46" s="67"/>
-      <c r="C46" s="302"/>
-      <c r="D46" s="302"/>
-      <c r="E46" s="302"/>
-      <c r="F46" s="302"/>
+      <c r="C46" s="319"/>
+      <c r="D46" s="319"/>
+      <c r="E46" s="319"/>
+      <c r="F46" s="319"/>
       <c r="G46" s="200" t="s">
         <v>369</v>
       </c>
@@ -18496,21 +18265,21 @@
         <v>370</v>
       </c>
       <c r="B47" s="67"/>
-      <c r="C47" s="303" t="s">
+      <c r="C47" s="318" t="s">
         <v>371</v>
       </c>
-      <c r="D47" s="303"/>
+      <c r="D47" s="318"/>
       <c r="E47" s="117"/>
       <c r="F47" s="118"/>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="338"/>
-      <c r="B48" s="339"/>
-      <c r="C48" s="339"/>
-      <c r="D48" s="339"/>
-      <c r="E48" s="339"/>
-      <c r="F48" s="340"/>
+      <c r="A48" s="369"/>
+      <c r="B48" s="370"/>
+      <c r="C48" s="370"/>
+      <c r="D48" s="370"/>
+      <c r="E48" s="370"/>
+      <c r="F48" s="371"/>
       <c r="G48" s="201" t="s">
         <v>369</v>
       </c>
@@ -18523,12 +18292,12 @@
       <c r="N48" s="73"/>
     </row>
     <row r="49" spans="1:14" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="341"/>
-      <c r="B49" s="342"/>
-      <c r="C49" s="342"/>
-      <c r="D49" s="342"/>
-      <c r="E49" s="342"/>
-      <c r="F49" s="343"/>
+      <c r="A49" s="372"/>
+      <c r="B49" s="373"/>
+      <c r="C49" s="373"/>
+      <c r="D49" s="373"/>
+      <c r="E49" s="373"/>
+      <c r="F49" s="374"/>
       <c r="G49" s="119"/>
       <c r="H49" s="115"/>
       <c r="I49" s="115"/>
@@ -18539,10 +18308,10 @@
       <c r="N49" s="73"/>
     </row>
     <row r="50" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="414" t="s">
+      <c r="A50" s="304" t="s">
         <v>372</v>
       </c>
-      <c r="B50" s="415"/>
+      <c r="B50" s="305"/>
       <c r="C50" s="197" t="s">
         <v>373</v>
       </c>
@@ -18552,145 +18321,127 @@
       <c r="G50" s="197"/>
       <c r="H50" s="197"/>
       <c r="I50" s="198"/>
-      <c r="J50" s="326"/>
-      <c r="K50" s="327"/>
-      <c r="L50" s="327"/>
-      <c r="M50" s="328"/>
+      <c r="J50" s="356"/>
+      <c r="K50" s="357"/>
+      <c r="L50" s="357"/>
+      <c r="M50" s="358"/>
     </row>
     <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="335" t="s">
+      <c r="A51" s="366" t="s">
         <v>374</v>
       </c>
-      <c r="B51" s="336"/>
-      <c r="C51" s="336"/>
-      <c r="D51" s="336"/>
-      <c r="E51" s="337"/>
+      <c r="B51" s="367"/>
+      <c r="C51" s="367"/>
+      <c r="D51" s="367"/>
+      <c r="E51" s="368"/>
       <c r="F51" s="278" t="s">
         <v>375</v>
       </c>
-      <c r="G51" s="344" t="s">
+      <c r="G51" s="375" t="s">
         <v>376</v>
       </c>
-      <c r="H51" s="345"/>
-      <c r="I51" s="346"/>
-      <c r="J51" s="329"/>
-      <c r="K51" s="330"/>
-      <c r="L51" s="330"/>
-      <c r="M51" s="331"/>
+      <c r="H51" s="376"/>
+      <c r="I51" s="377"/>
+      <c r="J51" s="359"/>
+      <c r="K51" s="360"/>
+      <c r="L51" s="360"/>
+      <c r="M51" s="361"/>
     </row>
     <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="354" t="s">
-        <v>421</v>
-      </c>
-      <c r="B52" s="355"/>
-      <c r="C52" s="357"/>
-      <c r="D52" s="357"/>
-      <c r="E52" s="358"/>
-      <c r="F52" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="G52" s="347">
-        <v>9175159197</v>
-      </c>
-      <c r="H52" s="348"/>
-      <c r="I52" s="349"/>
-      <c r="J52" s="329"/>
-      <c r="K52" s="330"/>
-      <c r="L52" s="330"/>
-      <c r="M52" s="331"/>
+      <c r="A52" s="387"/>
+      <c r="B52" s="388"/>
+      <c r="C52" s="390"/>
+      <c r="D52" s="390"/>
+      <c r="E52" s="391"/>
+      <c r="F52" s="74"/>
+      <c r="G52" s="380"/>
+      <c r="H52" s="381"/>
+      <c r="I52" s="382"/>
+      <c r="J52" s="359"/>
+      <c r="K52" s="360"/>
+      <c r="L52" s="360"/>
+      <c r="M52" s="361"/>
     </row>
     <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="354" t="s">
-        <v>423</v>
-      </c>
-      <c r="B53" s="355"/>
-      <c r="C53" s="355"/>
-      <c r="D53" s="355"/>
-      <c r="E53" s="356"/>
-      <c r="F53" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="G53" s="347">
-        <v>9178644951</v>
-      </c>
-      <c r="H53" s="348"/>
-      <c r="I53" s="349"/>
-      <c r="J53" s="329"/>
-      <c r="K53" s="330"/>
-      <c r="L53" s="330"/>
-      <c r="M53" s="331"/>
+      <c r="A53" s="387"/>
+      <c r="B53" s="388"/>
+      <c r="C53" s="388"/>
+      <c r="D53" s="388"/>
+      <c r="E53" s="389"/>
+      <c r="F53" s="74"/>
+      <c r="G53" s="380"/>
+      <c r="H53" s="381"/>
+      <c r="I53" s="382"/>
+      <c r="J53" s="359"/>
+      <c r="K53" s="360"/>
+      <c r="L53" s="360"/>
+      <c r="M53" s="361"/>
     </row>
     <row r="54" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="350" t="s">
-        <v>425</v>
-      </c>
-      <c r="B54" s="351"/>
-      <c r="C54" s="352"/>
-      <c r="D54" s="352"/>
-      <c r="E54" s="353"/>
-      <c r="F54" s="209" t="s">
-        <v>424</v>
-      </c>
-      <c r="G54" s="332">
-        <v>9178094456</v>
-      </c>
-      <c r="H54" s="333"/>
-      <c r="I54" s="334"/>
-      <c r="J54" s="329"/>
-      <c r="K54" s="330"/>
-      <c r="L54" s="330"/>
-      <c r="M54" s="331"/>
+      <c r="A54" s="383"/>
+      <c r="B54" s="384"/>
+      <c r="C54" s="385"/>
+      <c r="D54" s="385"/>
+      <c r="E54" s="386"/>
+      <c r="F54" s="209"/>
+      <c r="G54" s="363"/>
+      <c r="H54" s="364"/>
+      <c r="I54" s="365"/>
+      <c r="J54" s="359"/>
+      <c r="K54" s="360"/>
+      <c r="L54" s="360"/>
+      <c r="M54" s="361"/>
     </row>
     <row r="55" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="316" t="s">
+      <c r="A55" s="378" t="s">
         <v>377</v>
       </c>
-      <c r="B55" s="317"/>
-      <c r="C55" s="359" t="s">
+      <c r="B55" s="379"/>
+      <c r="C55" s="392" t="s">
         <v>397</v>
       </c>
-      <c r="D55" s="359"/>
-      <c r="E55" s="359"/>
-      <c r="F55" s="359"/>
-      <c r="G55" s="359"/>
-      <c r="H55" s="359"/>
+      <c r="D55" s="392"/>
+      <c r="E55" s="392"/>
+      <c r="F55" s="392"/>
+      <c r="G55" s="392"/>
+      <c r="H55" s="392"/>
       <c r="I55" s="266"/>
-      <c r="J55" s="330"/>
-      <c r="K55" s="330"/>
-      <c r="L55" s="330"/>
-      <c r="M55" s="331"/>
+      <c r="J55" s="360"/>
+      <c r="K55" s="360"/>
+      <c r="L55" s="360"/>
+      <c r="M55" s="361"/>
     </row>
     <row r="56" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="75"/>
       <c r="B56" s="76"/>
-      <c r="C56" s="360"/>
-      <c r="D56" s="360"/>
-      <c r="E56" s="360"/>
-      <c r="F56" s="360"/>
-      <c r="G56" s="360"/>
-      <c r="H56" s="360"/>
+      <c r="C56" s="393"/>
+      <c r="D56" s="393"/>
+      <c r="E56" s="393"/>
+      <c r="F56" s="393"/>
+      <c r="G56" s="393"/>
+      <c r="H56" s="393"/>
       <c r="I56" s="267"/>
       <c r="J56" s="208"/>
-      <c r="K56" s="298" t="s">
+      <c r="K56" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="L56" s="298"/>
+      <c r="L56" s="362"/>
       <c r="M56" s="188"/>
     </row>
     <row r="57" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="75"/>
       <c r="B57" s="76"/>
-      <c r="C57" s="360"/>
-      <c r="D57" s="360"/>
-      <c r="E57" s="360"/>
-      <c r="F57" s="360"/>
-      <c r="G57" s="360"/>
-      <c r="H57" s="360"/>
+      <c r="C57" s="393"/>
+      <c r="D57" s="393"/>
+      <c r="E57" s="393"/>
+      <c r="F57" s="393"/>
+      <c r="G57" s="393"/>
+      <c r="H57" s="393"/>
       <c r="I57" s="267"/>
-      <c r="J57" s="298"/>
-      <c r="K57" s="298"/>
-      <c r="L57" s="298"/>
-      <c r="M57" s="299"/>
+      <c r="J57" s="362"/>
+      <c r="K57" s="362"/>
+      <c r="L57" s="362"/>
+      <c r="M57" s="408"/>
     </row>
     <row r="58" spans="1:14" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="186"/>
@@ -18702,8 +18453,8 @@
       <c r="G58" s="268"/>
       <c r="H58" s="268"/>
       <c r="I58" s="269"/>
-      <c r="K58" s="385"/>
-      <c r="L58" s="386"/>
+      <c r="K58" s="342"/>
+      <c r="L58" s="343"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:14" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18715,106 +18466,102 @@
       <c r="G59" s="44"/>
       <c r="H59" s="44"/>
       <c r="I59" s="44"/>
-      <c r="K59" s="387"/>
-      <c r="L59" s="388"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="345"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:14" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="77"/>
-      <c r="B60" s="407" t="s">
+      <c r="B60" s="294" t="s">
         <v>398</v>
       </c>
-      <c r="C60" s="408"/>
-      <c r="D60" s="409"/>
-      <c r="F60" s="398" t="s">
-        <v>443</v>
-      </c>
-      <c r="G60" s="399"/>
-      <c r="H60" s="399"/>
-      <c r="I60" s="400"/>
-      <c r="K60" s="387"/>
-      <c r="L60" s="388"/>
+      <c r="C60" s="295"/>
+      <c r="D60" s="296"/>
+      <c r="F60" s="285"/>
+      <c r="G60" s="286"/>
+      <c r="H60" s="286"/>
+      <c r="I60" s="287"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="345"/>
       <c r="M60" s="78"/>
     </row>
     <row r="61" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="77"/>
-      <c r="B61" s="391" t="s">
+      <c r="B61" s="348" t="s">
         <v>379</v>
       </c>
-      <c r="C61" s="392"/>
-      <c r="D61" s="134" t="s">
-        <v>411</v>
-      </c>
-      <c r="F61" s="401"/>
-      <c r="G61" s="402"/>
-      <c r="H61" s="402"/>
-      <c r="I61" s="403"/>
-      <c r="K61" s="387"/>
-      <c r="L61" s="388"/>
+      <c r="C61" s="349"/>
+      <c r="D61" s="134"/>
+      <c r="F61" s="288"/>
+      <c r="G61" s="289"/>
+      <c r="H61" s="289"/>
+      <c r="I61" s="290"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="345"/>
       <c r="M61" s="78"/>
     </row>
     <row r="62" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="77"/>
-      <c r="B62" s="379" t="s">
+      <c r="B62" s="337" t="s">
         <v>380</v>
       </c>
-      <c r="C62" s="380"/>
-      <c r="D62" s="383"/>
-      <c r="F62" s="404"/>
-      <c r="G62" s="405"/>
-      <c r="H62" s="405"/>
-      <c r="I62" s="406"/>
-      <c r="K62" s="387"/>
-      <c r="L62" s="388"/>
+      <c r="C62" s="338"/>
+      <c r="D62" s="297"/>
+      <c r="F62" s="291"/>
+      <c r="G62" s="292"/>
+      <c r="H62" s="292"/>
+      <c r="I62" s="293"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="345"/>
       <c r="M62" s="78"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="77"/>
-      <c r="B63" s="393"/>
-      <c r="C63" s="394"/>
-      <c r="D63" s="410"/>
-      <c r="F63" s="411" t="s">
+      <c r="B63" s="350"/>
+      <c r="C63" s="351"/>
+      <c r="D63" s="298"/>
+      <c r="F63" s="299" t="s">
         <v>381</v>
       </c>
-      <c r="G63" s="412"/>
-      <c r="H63" s="412"/>
-      <c r="I63" s="413"/>
-      <c r="K63" s="387"/>
-      <c r="L63" s="388"/>
+      <c r="G63" s="300"/>
+      <c r="H63" s="300"/>
+      <c r="I63" s="301"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="345"/>
       <c r="M63" s="78"/>
     </row>
     <row r="64" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="77"/>
-      <c r="B64" s="379" t="s">
+      <c r="B64" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C64" s="380"/>
-      <c r="D64" s="383"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="297"/>
       <c r="F64" s="79"/>
       <c r="G64" s="189"/>
       <c r="H64" s="189"/>
       <c r="I64" s="190"/>
       <c r="J64" s="80"/>
-      <c r="K64" s="389"/>
-      <c r="L64" s="390"/>
+      <c r="K64" s="346"/>
+      <c r="L64" s="347"/>
       <c r="M64" s="78"/>
     </row>
     <row r="65" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="77"/>
-      <c r="B65" s="381"/>
-      <c r="C65" s="382"/>
-      <c r="D65" s="384"/>
-      <c r="F65" s="376" t="s">
+      <c r="B65" s="339"/>
+      <c r="C65" s="340"/>
+      <c r="D65" s="341"/>
+      <c r="F65" s="334" t="s">
         <v>383</v>
       </c>
-      <c r="G65" s="377"/>
-      <c r="H65" s="377"/>
-      <c r="I65" s="378"/>
+      <c r="G65" s="335"/>
+      <c r="H65" s="335"/>
+      <c r="I65" s="336"/>
       <c r="J65" s="80"/>
-      <c r="K65" s="374" t="s">
+      <c r="K65" s="332" t="s">
         <v>384</v>
       </c>
-      <c r="L65" s="375"/>
+      <c r="L65" s="333"/>
       <c r="M65" s="78"/>
     </row>
     <row r="66" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18833,32 +18580,32 @@
       <c r="M66" s="86"/>
     </row>
     <row r="67" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="371" t="s">
+      <c r="A67" s="329" t="s">
         <v>385</v>
       </c>
-      <c r="B67" s="372"/>
-      <c r="C67" s="372"/>
-      <c r="D67" s="372"/>
-      <c r="E67" s="372"/>
-      <c r="F67" s="372"/>
-      <c r="G67" s="372"/>
-      <c r="H67" s="372"/>
-      <c r="I67" s="372"/>
-      <c r="J67" s="372"/>
-      <c r="K67" s="372"/>
-      <c r="L67" s="372"/>
-      <c r="M67" s="373"/>
+      <c r="B67" s="330"/>
+      <c r="C67" s="330"/>
+      <c r="D67" s="330"/>
+      <c r="E67" s="330"/>
+      <c r="F67" s="330"/>
+      <c r="G67" s="330"/>
+      <c r="H67" s="330"/>
+      <c r="I67" s="330"/>
+      <c r="J67" s="330"/>
+      <c r="K67" s="330"/>
+      <c r="L67" s="330"/>
+      <c r="M67" s="331"/>
     </row>
     <row r="68" spans="1:13" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="77"/>
       <c r="B68" s="80"/>
       <c r="C68" s="87"/>
       <c r="D68" s="87"/>
-      <c r="E68" s="368"/>
-      <c r="F68" s="369"/>
-      <c r="G68" s="369"/>
-      <c r="H68" s="369"/>
-      <c r="I68" s="370"/>
+      <c r="E68" s="326"/>
+      <c r="F68" s="327"/>
+      <c r="G68" s="327"/>
+      <c r="H68" s="327"/>
+      <c r="I68" s="328"/>
       <c r="J68" s="135"/>
       <c r="K68" s="135"/>
       <c r="M68" s="78"/>
@@ -18868,13 +18615,13 @@
       <c r="B69" s="80"/>
       <c r="C69" s="251"/>
       <c r="D69" s="251"/>
-      <c r="E69" s="365" t="s">
+      <c r="E69" s="323" t="s">
         <v>386</v>
       </c>
-      <c r="F69" s="366"/>
-      <c r="G69" s="366"/>
-      <c r="H69" s="366"/>
-      <c r="I69" s="367"/>
+      <c r="F69" s="324"/>
+      <c r="G69" s="324"/>
+      <c r="H69" s="324"/>
+      <c r="I69" s="325"/>
       <c r="J69" s="137"/>
       <c r="K69" s="136"/>
       <c r="L69" s="88"/>
@@ -18896,21 +18643,21 @@
       <c r="M70" s="91"/>
     </row>
     <row r="71" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="364" t="s">
+      <c r="A71" s="322" t="s">
         <v>400</v>
       </c>
-      <c r="B71" s="364"/>
-      <c r="C71" s="364"/>
-      <c r="D71" s="364"/>
-      <c r="E71" s="364"/>
-      <c r="F71" s="364"/>
-      <c r="G71" s="364"/>
-      <c r="H71" s="364"/>
-      <c r="I71" s="364"/>
-      <c r="J71" s="364"/>
-      <c r="K71" s="364"/>
-      <c r="L71" s="364"/>
-      <c r="M71" s="364"/>
+      <c r="B71" s="322"/>
+      <c r="C71" s="322"/>
+      <c r="D71" s="322"/>
+      <c r="E71" s="322"/>
+      <c r="F71" s="322"/>
+      <c r="G71" s="322"/>
+      <c r="H71" s="322"/>
+      <c r="I71" s="322"/>
+      <c r="J71" s="322"/>
+      <c r="K71" s="322"/>
+      <c r="L71" s="322"/>
+      <c r="M71" s="322"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -18923,6 +18670,75 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="85">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F16"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C45:F46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="C37:F40"/>
+    <mergeCell ref="C41:F42"/>
+    <mergeCell ref="C43:F44"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:F30"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="J50:M55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A48:F49"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="C55:H57"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C31:F32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C34:F36"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="A67:M67"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="K58:L64"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C63"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="F60:I62"/>
@@ -18939,75 +18755,6 @@
     <mergeCell ref="G19:L19"/>
     <mergeCell ref="I25:L25"/>
     <mergeCell ref="C23:F26"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="E69:I69"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="A67:M67"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="K58:L64"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C63"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C31:F32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C34:F36"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="J50:M55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A48:F49"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="C55:H57"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C45:F46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="C37:F40"/>
-    <mergeCell ref="C41:F42"/>
-    <mergeCell ref="C43:F44"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:F30"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F16"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19644,13 +19391,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19885,27 +19631,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19930,9 +19668,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>